--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127053045</v>
       </c>
       <c r="B3" t="n">
-        <v>96614</v>
+        <v>96689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>127053050</v>
       </c>
       <c r="B4" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127053055</v>
       </c>
       <c r="B5" t="n">
-        <v>100543</v>
+        <v>100618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,45 +1098,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127053054</v>
+        <v>127053046</v>
       </c>
       <c r="B6" t="n">
-        <v>98361</v>
+        <v>96689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654699</v>
+        <v>654792</v>
       </c>
       <c r="R6" t="n">
-        <v>6648413</v>
+        <v>6648438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,6 +1189,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,57 +1208,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127053046</v>
+        <v>127053054</v>
       </c>
       <c r="B7" t="n">
-        <v>96614</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654792</v>
+        <v>654699</v>
       </c>
       <c r="R7" t="n">
-        <v>6648438</v>
+        <v>6648413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1287,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1305,45 +1305,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127053052</v>
+        <v>127053047</v>
       </c>
       <c r="B8" t="n">
-        <v>98361</v>
+        <v>96689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654680</v>
+        <v>654771</v>
       </c>
       <c r="R8" t="n">
-        <v>6648398</v>
+        <v>6648423</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,6 +1396,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,57 +1415,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127053047</v>
+        <v>127053052</v>
       </c>
       <c r="B9" t="n">
-        <v>96614</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654771</v>
+        <v>654680</v>
       </c>
       <c r="R9" t="n">
-        <v>6648423</v>
+        <v>6648398</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,7 +1494,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>127053049</v>
       </c>
       <c r="B10" t="n">
-        <v>91973</v>
+        <v>92047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>127053051</v>
       </c>
       <c r="B11" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>127126027</v>
       </c>
       <c r="B12" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>127125643</v>
       </c>
       <c r="B13" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127126120</v>
       </c>
       <c r="B14" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>127126282</v>
       </c>
       <c r="B15" t="n">
-        <v>96614</v>
+        <v>96689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127125022</v>
       </c>
       <c r="B16" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>127125864</v>
       </c>
       <c r="B18" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127125059</v>
       </c>
       <c r="B19" t="n">
-        <v>98278</v>
+        <v>98353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>127126407</v>
       </c>
       <c r="B20" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>127124755</v>
       </c>
       <c r="B21" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,38 +2965,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127123843</v>
+        <v>127124848</v>
       </c>
       <c r="B23" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654639</v>
+        <v>654727</v>
       </c>
       <c r="R23" t="n">
-        <v>6648349</v>
+        <v>6648365</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,38 +3077,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127124848</v>
+        <v>127123843</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654727</v>
+        <v>654639</v>
       </c>
       <c r="R24" t="n">
-        <v>6648365</v>
+        <v>6648349</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3304,7 +3304,7 @@
         <v>127124825</v>
       </c>
       <c r="B26" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127053045</v>
       </c>
       <c r="B3" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>127053050</v>
       </c>
       <c r="B4" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127053055</v>
       </c>
       <c r="B5" t="n">
-        <v>100618</v>
+        <v>100624</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>127053046</v>
       </c>
       <c r="B6" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>127053054</v>
       </c>
       <c r="B7" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
         <v>127053047</v>
       </c>
       <c r="B8" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         <v>127053052</v>
       </c>
       <c r="B9" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>127053049</v>
       </c>
       <c r="B10" t="n">
-        <v>92047</v>
+        <v>92053</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>127053051</v>
       </c>
       <c r="B11" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>127126027</v>
       </c>
       <c r="B12" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127125643</v>
+        <v>127126120</v>
       </c>
       <c r="B13" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1866,13 +1866,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654705</v>
+        <v>654740</v>
       </c>
       <c r="R13" t="n">
-        <v>6648385</v>
+        <v>6648381</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127126120</v>
+        <v>127125643</v>
       </c>
       <c r="B14" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1982,13 +1982,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654740</v>
+        <v>654705</v>
       </c>
       <c r="R14" t="n">
-        <v>6648381</v>
+        <v>6648385</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>127126282</v>
       </c>
       <c r="B15" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127125022</v>
       </c>
       <c r="B16" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>127125864</v>
       </c>
       <c r="B18" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127125059</v>
       </c>
       <c r="B19" t="n">
-        <v>98353</v>
+        <v>98359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>127126407</v>
       </c>
       <c r="B20" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>127124755</v>
       </c>
       <c r="B21" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,38 +2965,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127124848</v>
+        <v>127123843</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654727</v>
+        <v>654639</v>
       </c>
       <c r="R23" t="n">
-        <v>6648365</v>
+        <v>6648349</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,38 +3077,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127123843</v>
+        <v>127124848</v>
       </c>
       <c r="B24" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654639</v>
+        <v>654727</v>
       </c>
       <c r="R24" t="n">
-        <v>6648349</v>
+        <v>6648365</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3304,7 +3304,7 @@
         <v>127124825</v>
       </c>
       <c r="B26" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127123881</v>
+        <v>127124644</v>
       </c>
       <c r="B27" t="n">
-        <v>43935</v>
+        <v>5196</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654640</v>
+        <v>654725</v>
       </c>
       <c r="R27" t="n">
-        <v>6648354</v>
+        <v>6648334</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127124644</v>
+        <v>127123881</v>
       </c>
       <c r="B28" t="n">
-        <v>5196</v>
+        <v>43935</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654725</v>
+        <v>654640</v>
       </c>
       <c r="R28" t="n">
-        <v>6648334</v>
+        <v>6648354</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -1305,57 +1305,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127053047</v>
+        <v>127053052</v>
       </c>
       <c r="B8" t="n">
-        <v>96695</v>
+        <v>98442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654771</v>
+        <v>654680</v>
       </c>
       <c r="R8" t="n">
-        <v>6648423</v>
+        <v>6648398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1384,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1415,45 +1402,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127053052</v>
+        <v>127053047</v>
       </c>
       <c r="B9" t="n">
-        <v>98442</v>
+        <v>96695</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654680</v>
+        <v>654771</v>
       </c>
       <c r="R9" t="n">
-        <v>6648398</v>
+        <v>6648423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,6 +1493,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126120</v>
+        <v>127125643</v>
       </c>
       <c r="B13" t="n">
         <v>98442</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1866,13 +1866,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654740</v>
+        <v>654705</v>
       </c>
       <c r="R13" t="n">
-        <v>6648381</v>
+        <v>6648385</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127125643</v>
+        <v>127126120</v>
       </c>
       <c r="B14" t="n">
         <v>98442</v>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1982,13 +1982,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654705</v>
+        <v>654740</v>
       </c>
       <c r="R14" t="n">
-        <v>6648385</v>
+        <v>6648381</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127124644</v>
+        <v>127123881</v>
       </c>
       <c r="B27" t="n">
-        <v>5196</v>
+        <v>43935</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654725</v>
+        <v>654640</v>
       </c>
       <c r="R27" t="n">
-        <v>6648334</v>
+        <v>6648354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127123881</v>
+        <v>127124644</v>
       </c>
       <c r="B28" t="n">
-        <v>43935</v>
+        <v>5196</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654640</v>
+        <v>654725</v>
       </c>
       <c r="R28" t="n">
-        <v>6648354</v>
+        <v>6648334</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -904,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127053050</v>
+        <v>127053055</v>
       </c>
       <c r="B4" t="n">
-        <v>98442</v>
+        <v>100624</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654722</v>
+        <v>654681</v>
       </c>
       <c r="R4" t="n">
-        <v>6648435</v>
+        <v>6648407</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127053055</v>
+        <v>127053050</v>
       </c>
       <c r="B5" t="n">
-        <v>100624</v>
+        <v>98442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654681</v>
+        <v>654722</v>
       </c>
       <c r="R5" t="n">
-        <v>6648407</v>
+        <v>6648435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127053049</v>
+        <v>127053051</v>
       </c>
       <c r="B10" t="n">
-        <v>92053</v>
+        <v>98442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654713</v>
+        <v>654708</v>
       </c>
       <c r="R10" t="n">
-        <v>6648417</v>
+        <v>6648411</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127053051</v>
+        <v>127053049</v>
       </c>
       <c r="B11" t="n">
-        <v>98442</v>
+        <v>92053</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654708</v>
+        <v>654713</v>
       </c>
       <c r="R11" t="n">
-        <v>6648411</v>
+        <v>6648417</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127123881</v>
+        <v>127124644</v>
       </c>
       <c r="B27" t="n">
-        <v>43935</v>
+        <v>5196</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654640</v>
+        <v>654725</v>
       </c>
       <c r="R27" t="n">
-        <v>6648354</v>
+        <v>6648334</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127124644</v>
+        <v>127123881</v>
       </c>
       <c r="B28" t="n">
-        <v>5196</v>
+        <v>43935</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654725</v>
+        <v>654640</v>
       </c>
       <c r="R28" t="n">
-        <v>6648334</v>
+        <v>6648354</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127053045</v>
       </c>
       <c r="B3" t="n">
-        <v>96695</v>
+        <v>96696</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127053055</v>
+        <v>127053050</v>
       </c>
       <c r="B4" t="n">
-        <v>100624</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654681</v>
+        <v>654722</v>
       </c>
       <c r="R4" t="n">
-        <v>6648407</v>
+        <v>6648435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127053050</v>
+        <v>127053055</v>
       </c>
       <c r="B5" t="n">
-        <v>98442</v>
+        <v>100625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654722</v>
+        <v>654681</v>
       </c>
       <c r="R5" t="n">
-        <v>6648435</v>
+        <v>6648407</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,57 +1098,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127053046</v>
+        <v>127053054</v>
       </c>
       <c r="B6" t="n">
-        <v>96695</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654792</v>
+        <v>654699</v>
       </c>
       <c r="R6" t="n">
-        <v>6648438</v>
+        <v>6648413</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1177,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1208,45 +1195,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127053054</v>
+        <v>127053046</v>
       </c>
       <c r="B7" t="n">
-        <v>98442</v>
+        <v>96696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654699</v>
+        <v>654792</v>
       </c>
       <c r="R7" t="n">
-        <v>6648413</v>
+        <v>6648438</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,6 +1286,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>127053052</v>
       </c>
       <c r="B8" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1405,7 +1405,7 @@
         <v>127053047</v>
       </c>
       <c r="B9" t="n">
-        <v>96695</v>
+        <v>96696</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127053051</v>
+        <v>127053049</v>
       </c>
       <c r="B10" t="n">
-        <v>98442</v>
+        <v>92054</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654708</v>
+        <v>654713</v>
       </c>
       <c r="R10" t="n">
-        <v>6648411</v>
+        <v>6648417</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127053049</v>
+        <v>127053051</v>
       </c>
       <c r="B11" t="n">
-        <v>92053</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654713</v>
+        <v>654708</v>
       </c>
       <c r="R11" t="n">
-        <v>6648417</v>
+        <v>6648411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
         <v>127126027</v>
       </c>
       <c r="B12" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>127125643</v>
       </c>
       <c r="B13" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127126120</v>
       </c>
       <c r="B14" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>127126282</v>
       </c>
       <c r="B15" t="n">
-        <v>96695</v>
+        <v>96696</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127125022</v>
       </c>
       <c r="B16" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>127125864</v>
       </c>
       <c r="B18" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127125059</v>
       </c>
       <c r="B19" t="n">
-        <v>98359</v>
+        <v>98360</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>127126407</v>
       </c>
       <c r="B20" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>127124755</v>
       </c>
       <c r="B21" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>127124825</v>
       </c>
       <c r="B26" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127124644</v>
+        <v>127123881</v>
       </c>
       <c r="B27" t="n">
-        <v>5196</v>
+        <v>43935</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654725</v>
+        <v>654640</v>
       </c>
       <c r="R27" t="n">
-        <v>6648334</v>
+        <v>6648354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127123881</v>
+        <v>127124644</v>
       </c>
       <c r="B28" t="n">
-        <v>43935</v>
+        <v>5196</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654640</v>
+        <v>654725</v>
       </c>
       <c r="R28" t="n">
-        <v>6648354</v>
+        <v>6648334</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -1098,45 +1098,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127053054</v>
+        <v>127053046</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654699</v>
+        <v>654792</v>
       </c>
       <c r="R6" t="n">
-        <v>6648413</v>
+        <v>6648438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,6 +1189,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,57 +1208,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127053046</v>
+        <v>127053054</v>
       </c>
       <c r="B7" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654792</v>
+        <v>654699</v>
       </c>
       <c r="R7" t="n">
-        <v>6648438</v>
+        <v>6648413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1287,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1305,45 +1305,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127053052</v>
+        <v>127053047</v>
       </c>
       <c r="B8" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654680</v>
+        <v>654771</v>
       </c>
       <c r="R8" t="n">
-        <v>6648398</v>
+        <v>6648423</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,6 +1396,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,57 +1415,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127053047</v>
+        <v>127053052</v>
       </c>
       <c r="B9" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654771</v>
+        <v>654680</v>
       </c>
       <c r="R9" t="n">
-        <v>6648423</v>
+        <v>6648398</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,7 +1494,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -904,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127053050</v>
+        <v>127053055</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>100625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654722</v>
+        <v>654681</v>
       </c>
       <c r="R4" t="n">
-        <v>6648435</v>
+        <v>6648407</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127053055</v>
+        <v>127053050</v>
       </c>
       <c r="B5" t="n">
-        <v>100625</v>
+        <v>98443</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654681</v>
+        <v>654722</v>
       </c>
       <c r="R5" t="n">
-        <v>6648407</v>
+        <v>6648435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127053049</v>
+        <v>127053051</v>
       </c>
       <c r="B10" t="n">
-        <v>92054</v>
+        <v>98443</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654713</v>
+        <v>654708</v>
       </c>
       <c r="R10" t="n">
-        <v>6648417</v>
+        <v>6648411</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127053051</v>
+        <v>127053049</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>92054</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654708</v>
+        <v>654713</v>
       </c>
       <c r="R11" t="n">
-        <v>6648411</v>
+        <v>6648417</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1822,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127125643</v>
+        <v>127126120</v>
       </c>
       <c r="B13" t="n">
         <v>98443</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1866,13 +1866,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654705</v>
+        <v>654740</v>
       </c>
       <c r="R13" t="n">
-        <v>6648385</v>
+        <v>6648381</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127126120</v>
+        <v>127125643</v>
       </c>
       <c r="B14" t="n">
         <v>98443</v>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1982,13 +1982,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654740</v>
+        <v>654705</v>
       </c>
       <c r="R14" t="n">
-        <v>6648381</v>
+        <v>6648385</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2277,38 +2277,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125124</v>
+        <v>127125864</v>
       </c>
       <c r="B17" t="n">
-        <v>5196</v>
+        <v>98443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2317,13 +2321,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654705</v>
+        <v>654709</v>
       </c>
       <c r="R17" t="n">
-        <v>6648385</v>
+        <v>6648286</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2389,42 +2393,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127125864</v>
+        <v>127125124</v>
       </c>
       <c r="B18" t="n">
-        <v>98443</v>
+        <v>5196</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654709</v>
+        <v>654705</v>
       </c>
       <c r="R18" t="n">
-        <v>6648286</v>
+        <v>6648385</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127126407</v>
+        <v>127124755</v>
       </c>
       <c r="B20" t="n">
         <v>98443</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2665,13 +2665,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654783</v>
+        <v>654725</v>
       </c>
       <c r="R20" t="n">
-        <v>6648421</v>
+        <v>6648334</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,7 +2737,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127124755</v>
+        <v>127126407</v>
       </c>
       <c r="B21" t="n">
         <v>98443</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2781,13 +2781,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654725</v>
+        <v>654783</v>
       </c>
       <c r="R21" t="n">
-        <v>6648334</v>
+        <v>6648421</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,38 +2965,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127123843</v>
+        <v>127124848</v>
       </c>
       <c r="B23" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654639</v>
+        <v>654727</v>
       </c>
       <c r="R23" t="n">
-        <v>6648349</v>
+        <v>6648365</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,38 +3077,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127124848</v>
+        <v>127123843</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654727</v>
+        <v>654639</v>
       </c>
       <c r="R24" t="n">
-        <v>6648365</v>
+        <v>6648349</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3417,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127123881</v>
+        <v>127124644</v>
       </c>
       <c r="B27" t="n">
-        <v>43935</v>
+        <v>5196</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654640</v>
+        <v>654725</v>
       </c>
       <c r="R27" t="n">
-        <v>6648354</v>
+        <v>6648334</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127124644</v>
+        <v>127123881</v>
       </c>
       <c r="B28" t="n">
-        <v>5196</v>
+        <v>43935</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654725</v>
+        <v>654640</v>
       </c>
       <c r="R28" t="n">
-        <v>6648334</v>
+        <v>6648354</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127053051</v>
+        <v>127053049</v>
       </c>
       <c r="B10" t="n">
-        <v>98443</v>
+        <v>92054</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654708</v>
+        <v>654713</v>
       </c>
       <c r="R10" t="n">
-        <v>6648411</v>
+        <v>6648417</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127053049</v>
+        <v>127053051</v>
       </c>
       <c r="B11" t="n">
-        <v>92054</v>
+        <v>98443</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654713</v>
+        <v>654708</v>
       </c>
       <c r="R11" t="n">
-        <v>6648417</v>
+        <v>6648411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124755</v>
+        <v>127126407</v>
       </c>
       <c r="B20" t="n">
         <v>98443</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2665,13 +2665,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654725</v>
+        <v>654783</v>
       </c>
       <c r="R20" t="n">
-        <v>6648334</v>
+        <v>6648421</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,7 +2737,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127126407</v>
+        <v>127124755</v>
       </c>
       <c r="B21" t="n">
         <v>98443</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2781,13 +2781,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654783</v>
+        <v>654725</v>
       </c>
       <c r="R21" t="n">
-        <v>6648421</v>
+        <v>6648334</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,38 +2965,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127124848</v>
+        <v>127123843</v>
       </c>
       <c r="B23" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654727</v>
+        <v>654639</v>
       </c>
       <c r="R23" t="n">
-        <v>6648365</v>
+        <v>6648349</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,38 +3077,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127123843</v>
+        <v>127124848</v>
       </c>
       <c r="B24" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654639</v>
+        <v>654727</v>
       </c>
       <c r="R24" t="n">
-        <v>6648349</v>
+        <v>6648365</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3417,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127124644</v>
+        <v>127123881</v>
       </c>
       <c r="B27" t="n">
-        <v>5196</v>
+        <v>43935</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654725</v>
+        <v>654640</v>
       </c>
       <c r="R27" t="n">
-        <v>6648334</v>
+        <v>6648354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127123881</v>
+        <v>127124644</v>
       </c>
       <c r="B28" t="n">
-        <v>43935</v>
+        <v>5196</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654640</v>
+        <v>654725</v>
       </c>
       <c r="R28" t="n">
-        <v>6648354</v>
+        <v>6648334</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -904,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127053055</v>
+        <v>127053050</v>
       </c>
       <c r="B4" t="n">
-        <v>100625</v>
+        <v>98443</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654681</v>
+        <v>654722</v>
       </c>
       <c r="R4" t="n">
-        <v>6648407</v>
+        <v>6648435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127053050</v>
+        <v>127053055</v>
       </c>
       <c r="B5" t="n">
-        <v>98443</v>
+        <v>100625</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654722</v>
+        <v>654681</v>
       </c>
       <c r="R5" t="n">
-        <v>6648435</v>
+        <v>6648407</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,57 +1098,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127053046</v>
+        <v>127053054</v>
       </c>
       <c r="B6" t="n">
-        <v>96696</v>
+        <v>98443</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654792</v>
+        <v>654699</v>
       </c>
       <c r="R6" t="n">
-        <v>6648438</v>
+        <v>6648413</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1177,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1208,45 +1195,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127053054</v>
+        <v>127053046</v>
       </c>
       <c r="B7" t="n">
-        <v>98443</v>
+        <v>96696</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654699</v>
+        <v>654792</v>
       </c>
       <c r="R7" t="n">
-        <v>6648413</v>
+        <v>6648438</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,6 +1286,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127053045</v>
       </c>
       <c r="B3" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>127053050</v>
       </c>
       <c r="B4" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127053055</v>
       </c>
       <c r="B5" t="n">
-        <v>100625</v>
+        <v>100629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,45 +1098,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127053054</v>
+        <v>127053046</v>
       </c>
       <c r="B6" t="n">
-        <v>98443</v>
+        <v>96700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654699</v>
+        <v>654792</v>
       </c>
       <c r="R6" t="n">
-        <v>6648413</v>
+        <v>6648438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,6 +1189,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,57 +1208,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127053046</v>
+        <v>127053054</v>
       </c>
       <c r="B7" t="n">
-        <v>96696</v>
+        <v>98447</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654792</v>
+        <v>654699</v>
       </c>
       <c r="R7" t="n">
-        <v>6648438</v>
+        <v>6648413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1287,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1305,57 +1305,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127053047</v>
+        <v>127053052</v>
       </c>
       <c r="B8" t="n">
-        <v>96696</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654771</v>
+        <v>654680</v>
       </c>
       <c r="R8" t="n">
-        <v>6648423</v>
+        <v>6648398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1384,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1415,45 +1402,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127053052</v>
+        <v>127053047</v>
       </c>
       <c r="B9" t="n">
-        <v>98443</v>
+        <v>96700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654680</v>
+        <v>654771</v>
       </c>
       <c r="R9" t="n">
-        <v>6648398</v>
+        <v>6648423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,6 +1493,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127053049</v>
+        <v>127053051</v>
       </c>
       <c r="B10" t="n">
-        <v>92054</v>
+        <v>98447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654713</v>
+        <v>654708</v>
       </c>
       <c r="R10" t="n">
-        <v>6648417</v>
+        <v>6648411</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127053051</v>
+        <v>127053049</v>
       </c>
       <c r="B11" t="n">
-        <v>98443</v>
+        <v>92058</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654708</v>
+        <v>654713</v>
       </c>
       <c r="R11" t="n">
-        <v>6648411</v>
+        <v>6648417</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
         <v>127126027</v>
       </c>
       <c r="B12" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1822,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127126120</v>
+        <v>127125643</v>
       </c>
       <c r="B13" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1866,13 +1866,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654740</v>
+        <v>654705</v>
       </c>
       <c r="R13" t="n">
-        <v>6648381</v>
+        <v>6648385</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1938,10 +1938,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127125643</v>
+        <v>127126120</v>
       </c>
       <c r="B14" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1968,7 +1968,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1982,13 +1982,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654705</v>
+        <v>654740</v>
       </c>
       <c r="R14" t="n">
-        <v>6648385</v>
+        <v>6648381</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>127126282</v>
       </c>
       <c r="B15" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127125022</v>
       </c>
       <c r="B16" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2277,42 +2277,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125864</v>
+        <v>127125124</v>
       </c>
       <c r="B17" t="n">
-        <v>98443</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2321,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654709</v>
+        <v>654705</v>
       </c>
       <c r="R17" t="n">
-        <v>6648286</v>
+        <v>6648385</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2393,38 +2389,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127125124</v>
+        <v>127125864</v>
       </c>
       <c r="B18" t="n">
-        <v>5196</v>
+        <v>98447</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654705</v>
+        <v>654709</v>
       </c>
       <c r="R18" t="n">
-        <v>6648385</v>
+        <v>6648286</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127125059</v>
       </c>
       <c r="B19" t="n">
-        <v>98360</v>
+        <v>98364</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2621,10 +2621,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127126407</v>
+        <v>127124755</v>
       </c>
       <c r="B20" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2665,13 +2665,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654783</v>
+        <v>654725</v>
       </c>
       <c r="R20" t="n">
-        <v>6648421</v>
+        <v>6648334</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,10 +2737,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127124755</v>
+        <v>127126407</v>
       </c>
       <c r="B21" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2781,13 +2781,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654725</v>
+        <v>654783</v>
       </c>
       <c r="R21" t="n">
-        <v>6648334</v>
+        <v>6648421</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2856,7 +2856,7 @@
         <v>127125737</v>
       </c>
       <c r="B22" t="n">
-        <v>5196</v>
+        <v>5197</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,38 +2965,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127123843</v>
+        <v>127124848</v>
       </c>
       <c r="B23" t="n">
-        <v>57654</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654639</v>
+        <v>654727</v>
       </c>
       <c r="R23" t="n">
-        <v>6648349</v>
+        <v>6648365</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,38 +3077,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127124848</v>
+        <v>127123843</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>57658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654727</v>
+        <v>654639</v>
       </c>
       <c r="R24" t="n">
-        <v>6648365</v>
+        <v>6648349</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3192,7 +3192,7 @@
         <v>127125758</v>
       </c>
       <c r="B25" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>127124825</v>
       </c>
       <c r="B26" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127123881</v>
+        <v>127124644</v>
       </c>
       <c r="B27" t="n">
-        <v>43935</v>
+        <v>5197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654640</v>
+        <v>654725</v>
       </c>
       <c r="R27" t="n">
-        <v>6648354</v>
+        <v>6648334</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127124644</v>
+        <v>127123881</v>
       </c>
       <c r="B28" t="n">
-        <v>5196</v>
+        <v>43939</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654725</v>
+        <v>654640</v>
       </c>
       <c r="R28" t="n">
-        <v>6648334</v>
+        <v>6648354</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3644,7 +3644,7 @@
         <v>127124616</v>
       </c>
       <c r="B29" t="n">
-        <v>5176</v>
+        <v>5177</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -1305,45 +1305,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127053052</v>
+        <v>127053047</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654680</v>
+        <v>654771</v>
       </c>
       <c r="R8" t="n">
-        <v>6648398</v>
+        <v>6648423</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,6 +1396,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,57 +1415,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127053047</v>
+        <v>127053052</v>
       </c>
       <c r="B9" t="n">
-        <v>96700</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654771</v>
+        <v>654680</v>
       </c>
       <c r="R9" t="n">
-        <v>6648423</v>
+        <v>6648398</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,7 +1494,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127053051</v>
+        <v>127053049</v>
       </c>
       <c r="B10" t="n">
-        <v>98447</v>
+        <v>92058</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654708</v>
+        <v>654713</v>
       </c>
       <c r="R10" t="n">
-        <v>6648411</v>
+        <v>6648417</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127053049</v>
+        <v>127053051</v>
       </c>
       <c r="B11" t="n">
-        <v>92058</v>
+        <v>98447</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654713</v>
+        <v>654708</v>
       </c>
       <c r="R11" t="n">
-        <v>6648417</v>
+        <v>6648411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -2621,7 +2621,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127124755</v>
+        <v>127126407</v>
       </c>
       <c r="B20" t="n">
         <v>98447</v>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>56</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2665,13 +2665,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654725</v>
+        <v>654783</v>
       </c>
       <c r="R20" t="n">
-        <v>6648334</v>
+        <v>6648421</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2710,7 +2710,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,7 +2737,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127126407</v>
+        <v>127124755</v>
       </c>
       <c r="B21" t="n">
         <v>98447</v>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2781,13 +2781,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654783</v>
+        <v>654725</v>
       </c>
       <c r="R21" t="n">
-        <v>6648421</v>
+        <v>6648334</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,38 +2965,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127124848</v>
+        <v>127123843</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654727</v>
+        <v>654639</v>
       </c>
       <c r="R23" t="n">
-        <v>6648365</v>
+        <v>6648349</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,38 +3077,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127123843</v>
+        <v>127124848</v>
       </c>
       <c r="B24" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654639</v>
+        <v>654727</v>
       </c>
       <c r="R24" t="n">
-        <v>6648349</v>
+        <v>6648365</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3417,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127124644</v>
+        <v>127123881</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>43939</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654725</v>
+        <v>654640</v>
       </c>
       <c r="R27" t="n">
-        <v>6648334</v>
+        <v>6648354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127123881</v>
+        <v>127124644</v>
       </c>
       <c r="B28" t="n">
-        <v>43939</v>
+        <v>5197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654640</v>
+        <v>654725</v>
       </c>
       <c r="R28" t="n">
-        <v>6648354</v>
+        <v>6648334</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -1305,57 +1305,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127053047</v>
+        <v>127053052</v>
       </c>
       <c r="B8" t="n">
-        <v>96700</v>
+        <v>98447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654771</v>
+        <v>654680</v>
       </c>
       <c r="R8" t="n">
-        <v>6648423</v>
+        <v>6648398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1384,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1415,45 +1402,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127053052</v>
+        <v>127053047</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654680</v>
+        <v>654771</v>
       </c>
       <c r="R9" t="n">
-        <v>6648398</v>
+        <v>6648423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,6 +1493,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -1305,45 +1305,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127053052</v>
+        <v>127053047</v>
       </c>
       <c r="B8" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654680</v>
+        <v>654771</v>
       </c>
       <c r="R8" t="n">
-        <v>6648398</v>
+        <v>6648423</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,6 +1396,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,57 +1415,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127053047</v>
+        <v>127053052</v>
       </c>
       <c r="B9" t="n">
-        <v>96700</v>
+        <v>98447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654771</v>
+        <v>654680</v>
       </c>
       <c r="R9" t="n">
-        <v>6648423</v>
+        <v>6648398</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,7 +1494,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -904,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127053050</v>
+        <v>127053055</v>
       </c>
       <c r="B4" t="n">
-        <v>98447</v>
+        <v>100630</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654722</v>
+        <v>654681</v>
       </c>
       <c r="R4" t="n">
-        <v>6648435</v>
+        <v>6648407</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127053055</v>
+        <v>127053050</v>
       </c>
       <c r="B5" t="n">
-        <v>100629</v>
+        <v>98448</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654681</v>
+        <v>654722</v>
       </c>
       <c r="R5" t="n">
-        <v>6648407</v>
+        <v>6648435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1098,57 +1098,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127053046</v>
+        <v>127053054</v>
       </c>
       <c r="B6" t="n">
-        <v>96700</v>
+        <v>98448</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654792</v>
+        <v>654699</v>
       </c>
       <c r="R6" t="n">
-        <v>6648438</v>
+        <v>6648413</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1177,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1208,45 +1195,57 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127053054</v>
+        <v>127053046</v>
       </c>
       <c r="B7" t="n">
-        <v>98447</v>
+        <v>96700</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654699</v>
+        <v>654792</v>
       </c>
       <c r="R7" t="n">
-        <v>6648413</v>
+        <v>6648438</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,6 +1286,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1418,7 +1418,7 @@
         <v>127053052</v>
       </c>
       <c r="B9" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>127053051</v>
       </c>
       <c r="B11" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>127126027</v>
       </c>
       <c r="B12" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>127125643</v>
       </c>
       <c r="B13" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127126120</v>
       </c>
       <c r="B14" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127125022</v>
       </c>
       <c r="B16" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>127125864</v>
       </c>
       <c r="B18" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127125059</v>
       </c>
       <c r="B19" t="n">
-        <v>98364</v>
+        <v>98365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>127126407</v>
       </c>
       <c r="B20" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>127124755</v>
       </c>
       <c r="B21" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>127124825</v>
       </c>
       <c r="B26" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -1098,45 +1098,57 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127053054</v>
+        <v>127053046</v>
       </c>
       <c r="B6" t="n">
-        <v>98448</v>
+        <v>96700</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654699</v>
+        <v>654792</v>
       </c>
       <c r="R6" t="n">
-        <v>6648413</v>
+        <v>6648438</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1177,6 +1189,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1195,57 +1208,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127053046</v>
+        <v>127053054</v>
       </c>
       <c r="B7" t="n">
-        <v>96700</v>
+        <v>98448</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654792</v>
+        <v>654699</v>
       </c>
       <c r="R7" t="n">
-        <v>6648438</v>
+        <v>6648413</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1287,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127053045</v>
       </c>
       <c r="B3" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>127053055</v>
       </c>
       <c r="B4" t="n">
-        <v>100630</v>
+        <v>100632</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127053050</v>
       </c>
       <c r="B5" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>127053046</v>
       </c>
       <c r="B6" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>127053054</v>
       </c>
       <c r="B7" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,57 +1305,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127053047</v>
+        <v>127053052</v>
       </c>
       <c r="B8" t="n">
-        <v>96700</v>
+        <v>98450</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654771</v>
+        <v>654680</v>
       </c>
       <c r="R8" t="n">
-        <v>6648423</v>
+        <v>6648398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1384,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1415,45 +1402,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127053052</v>
+        <v>127053047</v>
       </c>
       <c r="B9" t="n">
-        <v>98448</v>
+        <v>96702</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654680</v>
+        <v>654771</v>
       </c>
       <c r="R9" t="n">
-        <v>6648398</v>
+        <v>6648423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,6 +1493,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>127053049</v>
       </c>
       <c r="B10" t="n">
-        <v>92058</v>
+        <v>92060</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>127053051</v>
       </c>
       <c r="B11" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>127126027</v>
       </c>
       <c r="B12" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>127125643</v>
       </c>
       <c r="B13" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127126120</v>
       </c>
       <c r="B14" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>127126282</v>
       </c>
       <c r="B15" t="n">
-        <v>96700</v>
+        <v>96702</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127125022</v>
       </c>
       <c r="B16" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>127125864</v>
       </c>
       <c r="B18" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127125059</v>
       </c>
       <c r="B19" t="n">
-        <v>98365</v>
+        <v>98367</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>127126407</v>
       </c>
       <c r="B20" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>127124755</v>
       </c>
       <c r="B21" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2965,38 +2965,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127123843</v>
+        <v>127124848</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654639</v>
+        <v>654727</v>
       </c>
       <c r="R23" t="n">
-        <v>6648349</v>
+        <v>6648365</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,38 +3077,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127124848</v>
+        <v>127123843</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654727</v>
+        <v>654639</v>
       </c>
       <c r="R24" t="n">
-        <v>6648365</v>
+        <v>6648349</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3192,7 +3192,7 @@
         <v>127125758</v>
       </c>
       <c r="B25" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>127124825</v>
       </c>
       <c r="B26" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>127123881</v>
       </c>
       <c r="B27" t="n">
-        <v>43939</v>
+        <v>43941</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -904,32 +904,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127053055</v>
+        <v>127053050</v>
       </c>
       <c r="B4" t="n">
-        <v>100632</v>
+        <v>98450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222498</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654681</v>
+        <v>654722</v>
       </c>
       <c r="R4" t="n">
-        <v>6648407</v>
+        <v>6648435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1001,32 +1001,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127053050</v>
+        <v>127053055</v>
       </c>
       <c r="B5" t="n">
-        <v>98450</v>
+        <v>100632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>222498</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654722</v>
+        <v>654681</v>
       </c>
       <c r="R5" t="n">
-        <v>6648435</v>
+        <v>6648407</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -2277,38 +2277,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125124</v>
+        <v>127125864</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>98450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2317,13 +2321,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654705</v>
+        <v>654709</v>
       </c>
       <c r="R17" t="n">
-        <v>6648385</v>
+        <v>6648286</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2389,42 +2393,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127125864</v>
+        <v>127125124</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>5197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654709</v>
+        <v>654705</v>
       </c>
       <c r="R18" t="n">
-        <v>6648286</v>
+        <v>6648385</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2965,38 +2965,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127124848</v>
+        <v>127123843</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654727</v>
+        <v>654639</v>
       </c>
       <c r="R23" t="n">
-        <v>6648365</v>
+        <v>6648349</v>
       </c>
       <c r="S23" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,38 +3077,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127123843</v>
+        <v>127124848</v>
       </c>
       <c r="B24" t="n">
-        <v>57660</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654639</v>
+        <v>654727</v>
       </c>
       <c r="R24" t="n">
-        <v>6648349</v>
+        <v>6648365</v>
       </c>
       <c r="S24" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY29"/>
+  <dimension ref="A1:AY39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2277,42 +2277,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125864</v>
+        <v>127125124</v>
       </c>
       <c r="B17" t="n">
-        <v>98450</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2321,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654709</v>
+        <v>654705</v>
       </c>
       <c r="R17" t="n">
-        <v>6648286</v>
+        <v>6648385</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2393,38 +2389,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127125124</v>
+        <v>127125864</v>
       </c>
       <c r="B18" t="n">
-        <v>5197</v>
+        <v>98450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654705</v>
+        <v>654709</v>
       </c>
       <c r="R18" t="n">
-        <v>6648385</v>
+        <v>6648286</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -3751,6 +3751,1135 @@
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127785029</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>654805</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6648382</v>
+      </c>
+      <c r="S30" t="n">
+        <v>7</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>20:08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Minst 50-talet bladrosetter.</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>127785015</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>654819</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6648392</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>127785435</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>654700</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6648457</v>
+      </c>
+      <c r="S32" t="n">
+        <v>15</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>20:31</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>127784839</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>654838</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6648421</v>
+      </c>
+      <c r="S33" t="n">
+        <v>12</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>20:03</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>127785662</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>654746</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6648486</v>
+      </c>
+      <c r="S34" t="n">
+        <v>9</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>20:38</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127785113</v>
+      </c>
+      <c r="B35" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>654803</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6648362</v>
+      </c>
+      <c r="S35" t="n">
+        <v>8</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127784998</v>
+      </c>
+      <c r="B36" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>654833</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6648417</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127785496</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>654725</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6648468</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127785128</v>
+      </c>
+      <c r="B38" t="n">
+        <v>105488</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>654803</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6648362</v>
+      </c>
+      <c r="S38" t="n">
+        <v>8</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>127785306</v>
+      </c>
+      <c r="B39" t="n">
+        <v>98450</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>654761</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6648341</v>
+      </c>
+      <c r="S39" t="n">
+        <v>5</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -1305,45 +1305,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127053052</v>
+        <v>127053047</v>
       </c>
       <c r="B8" t="n">
-        <v>98450</v>
+        <v>96702</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654680</v>
+        <v>654771</v>
       </c>
       <c r="R8" t="n">
-        <v>6648398</v>
+        <v>6648423</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,6 +1396,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,57 +1415,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127053047</v>
+        <v>127053052</v>
       </c>
       <c r="B9" t="n">
-        <v>96702</v>
+        <v>98450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654771</v>
+        <v>654680</v>
       </c>
       <c r="R9" t="n">
-        <v>6648423</v>
+        <v>6648398</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,7 +1494,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127053045</v>
       </c>
       <c r="B3" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>127053050</v>
       </c>
       <c r="B4" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127053055</v>
       </c>
       <c r="B5" t="n">
-        <v>100632</v>
+        <v>100638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>127053046</v>
       </c>
       <c r="B6" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>127053054</v>
       </c>
       <c r="B7" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,57 +1305,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127053047</v>
+        <v>127053052</v>
       </c>
       <c r="B8" t="n">
-        <v>96702</v>
+        <v>98456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654771</v>
+        <v>654680</v>
       </c>
       <c r="R8" t="n">
-        <v>6648423</v>
+        <v>6648398</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1396,7 +1384,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1415,45 +1402,57 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127053052</v>
+        <v>127053047</v>
       </c>
       <c r="B9" t="n">
-        <v>98450</v>
+        <v>96708</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654680</v>
+        <v>654771</v>
       </c>
       <c r="R9" t="n">
-        <v>6648398</v>
+        <v>6648423</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1494,6 +1493,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127053049</v>
+        <v>127053051</v>
       </c>
       <c r="B10" t="n">
-        <v>92060</v>
+        <v>98456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654713</v>
+        <v>654708</v>
       </c>
       <c r="R10" t="n">
-        <v>6648417</v>
+        <v>6648411</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127053051</v>
+        <v>127053049</v>
       </c>
       <c r="B11" t="n">
-        <v>98450</v>
+        <v>92066</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654708</v>
+        <v>654713</v>
       </c>
       <c r="R11" t="n">
-        <v>6648411</v>
+        <v>6648417</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
         <v>127126027</v>
       </c>
       <c r="B12" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>127125643</v>
       </c>
       <c r="B13" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127126120</v>
       </c>
       <c r="B14" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>127126282</v>
       </c>
       <c r="B15" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127125022</v>
       </c>
       <c r="B16" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2277,38 +2277,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125124</v>
+        <v>127125864</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>98456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2317,13 +2321,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654705</v>
+        <v>654709</v>
       </c>
       <c r="R17" t="n">
-        <v>6648385</v>
+        <v>6648286</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2389,42 +2393,38 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127125864</v>
+        <v>127125124</v>
       </c>
       <c r="B18" t="n">
-        <v>98450</v>
+        <v>5197</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654709</v>
+        <v>654705</v>
       </c>
       <c r="R18" t="n">
-        <v>6648286</v>
+        <v>6648385</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127125059</v>
       </c>
       <c r="B19" t="n">
-        <v>98367</v>
+        <v>98373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>127126407</v>
       </c>
       <c r="B20" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>127124755</v>
       </c>
       <c r="B21" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>127124825</v>
       </c>
       <c r="B26" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>127785029</v>
       </c>
       <c r="B30" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>127785015</v>
       </c>
       <c r="B31" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>127785435</v>
       </c>
       <c r="B32" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>127784839</v>
       </c>
       <c r="B33" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>127785662</v>
       </c>
       <c r="B34" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>127785113</v>
       </c>
       <c r="B35" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>127784998</v>
       </c>
       <c r="B36" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>127785496</v>
       </c>
       <c r="B37" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>127785128</v>
       </c>
       <c r="B38" t="n">
-        <v>105488</v>
+        <v>105494</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>127785306</v>
       </c>
       <c r="B39" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>127126027</v>
       </c>
       <c r="B12" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>127125643</v>
       </c>
       <c r="B13" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127126120</v>
       </c>
       <c r="B14" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>127126282</v>
       </c>
       <c r="B15" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127125022</v>
       </c>
       <c r="B16" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>127125864</v>
       </c>
       <c r="B17" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127125059</v>
       </c>
       <c r="B19" t="n">
-        <v>98373</v>
+        <v>98376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>127126407</v>
       </c>
       <c r="B20" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>127124755</v>
       </c>
       <c r="B21" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>127123843</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>127125758</v>
       </c>
       <c r="B25" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>127124825</v>
       </c>
       <c r="B26" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127123881</v>
+        <v>127124644</v>
       </c>
       <c r="B27" t="n">
-        <v>43941</v>
+        <v>5197</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654640</v>
+        <v>654725</v>
       </c>
       <c r="R27" t="n">
-        <v>6648354</v>
+        <v>6648334</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127124644</v>
+        <v>127123881</v>
       </c>
       <c r="B28" t="n">
-        <v>5197</v>
+        <v>43942</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654725</v>
+        <v>654640</v>
       </c>
       <c r="R28" t="n">
-        <v>6648334</v>
+        <v>6648354</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3756,7 +3756,7 @@
         <v>127785029</v>
       </c>
       <c r="B30" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>127785015</v>
       </c>
       <c r="B31" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>127785435</v>
       </c>
       <c r="B32" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>127784839</v>
       </c>
       <c r="B33" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>127785662</v>
       </c>
       <c r="B34" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>127785113</v>
       </c>
       <c r="B35" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>127784998</v>
       </c>
       <c r="B36" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>127785496</v>
       </c>
       <c r="B37" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>127785128</v>
       </c>
       <c r="B38" t="n">
-        <v>105494</v>
+        <v>105497</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>127785306</v>
       </c>
       <c r="B39" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>127126027</v>
       </c>
       <c r="B12" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>127125643</v>
       </c>
       <c r="B13" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127126120</v>
       </c>
       <c r="B14" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>127126282</v>
       </c>
       <c r="B15" t="n">
-        <v>96711</v>
+        <v>96719</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127125022</v>
       </c>
       <c r="B16" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2277,42 +2277,38 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125864</v>
+        <v>127125124</v>
       </c>
       <c r="B17" t="n">
-        <v>98459</v>
+        <v>5197</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2321,13 +2317,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654709</v>
+        <v>654705</v>
       </c>
       <c r="R17" t="n">
-        <v>6648286</v>
+        <v>6648385</v>
       </c>
       <c r="S17" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2393,38 +2389,42 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127125124</v>
+        <v>127125864</v>
       </c>
       <c r="B18" t="n">
-        <v>5197</v>
+        <v>98467</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2433,13 +2433,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654705</v>
+        <v>654709</v>
       </c>
       <c r="R18" t="n">
-        <v>6648385</v>
+        <v>6648286</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127125059</v>
       </c>
       <c r="B19" t="n">
-        <v>98376</v>
+        <v>98384</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>127126407</v>
       </c>
       <c r="B20" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>127124755</v>
       </c>
       <c r="B21" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2968,7 +2968,7 @@
         <v>127123843</v>
       </c>
       <c r="B23" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
         <v>127125758</v>
       </c>
       <c r="B25" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>127124825</v>
       </c>
       <c r="B26" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3417,10 +3417,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127124644</v>
+        <v>127123881</v>
       </c>
       <c r="B27" t="n">
-        <v>5197</v>
+        <v>43942</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3428,21 +3428,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654725</v>
+        <v>654640</v>
       </c>
       <c r="R27" t="n">
-        <v>6648334</v>
+        <v>6648354</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3529,10 +3529,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127123881</v>
+        <v>127124644</v>
       </c>
       <c r="B28" t="n">
-        <v>43942</v>
+        <v>5197</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3540,21 +3540,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>101735</v>
+        <v>105930</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3569,10 +3569,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654640</v>
+        <v>654725</v>
       </c>
       <c r="R28" t="n">
-        <v>6648354</v>
+        <v>6648334</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3756,7 +3756,7 @@
         <v>127785029</v>
       </c>
       <c r="B30" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>127785015</v>
       </c>
       <c r="B31" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>127785435</v>
       </c>
       <c r="B32" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>127784839</v>
       </c>
       <c r="B33" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>127785662</v>
       </c>
       <c r="B34" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>127785113</v>
       </c>
       <c r="B35" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>127784998</v>
       </c>
       <c r="B36" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>127785496</v>
       </c>
       <c r="B37" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>127785128</v>
       </c>
       <c r="B38" t="n">
-        <v>105497</v>
+        <v>105505</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>127785306</v>
       </c>
       <c r="B39" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -3756,7 +3756,7 @@
         <v>127785029</v>
       </c>
       <c r="B30" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>127785015</v>
       </c>
       <c r="B31" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>127785435</v>
       </c>
       <c r="B32" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>127784839</v>
       </c>
       <c r="B33" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>127785662</v>
       </c>
       <c r="B34" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>127785113</v>
       </c>
       <c r="B35" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>127784998</v>
       </c>
       <c r="B36" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>127785496</v>
       </c>
       <c r="B37" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>127785128</v>
       </c>
       <c r="B38" t="n">
-        <v>105505</v>
+        <v>105506</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>127785306</v>
       </c>
       <c r="B39" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -3756,7 +3756,7 @@
         <v>127785029</v>
       </c>
       <c r="B30" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>127785015</v>
       </c>
       <c r="B31" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>127785435</v>
       </c>
       <c r="B32" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>127784839</v>
       </c>
       <c r="B33" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>127785662</v>
       </c>
       <c r="B34" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>127785113</v>
       </c>
       <c r="B35" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>127784998</v>
       </c>
       <c r="B36" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>127785496</v>
       </c>
       <c r="B37" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>127785128</v>
       </c>
       <c r="B38" t="n">
-        <v>105506</v>
+        <v>105507</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>127785306</v>
       </c>
       <c r="B39" t="n">
-        <v>98468</v>
+        <v>98469</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -3756,7 +3756,7 @@
         <v>127785029</v>
       </c>
       <c r="B30" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>127785015</v>
       </c>
       <c r="B31" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>127785435</v>
       </c>
       <c r="B32" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>127784839</v>
       </c>
       <c r="B33" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>127785662</v>
       </c>
       <c r="B34" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>127785113</v>
       </c>
       <c r="B35" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>127784998</v>
       </c>
       <c r="B36" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>127785496</v>
       </c>
       <c r="B37" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>127785128</v>
       </c>
       <c r="B38" t="n">
-        <v>105507</v>
+        <v>105508</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>127785306</v>
       </c>
       <c r="B39" t="n">
-        <v>98469</v>
+        <v>98470</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -3756,7 +3756,7 @@
         <v>127785029</v>
       </c>
       <c r="B30" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>127785015</v>
       </c>
       <c r="B31" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>127785435</v>
       </c>
       <c r="B32" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>127784839</v>
       </c>
       <c r="B33" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>127785662</v>
       </c>
       <c r="B34" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>127785113</v>
       </c>
       <c r="B35" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>127784998</v>
       </c>
       <c r="B36" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>127785496</v>
       </c>
       <c r="B37" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>127785128</v>
       </c>
       <c r="B38" t="n">
-        <v>105508</v>
+        <v>105516</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>127785306</v>
       </c>
       <c r="B39" t="n">
-        <v>98470</v>
+        <v>98478</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -3756,7 +3756,7 @@
         <v>127785029</v>
       </c>
       <c r="B30" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3873,7 +3873,7 @@
         <v>127785015</v>
       </c>
       <c r="B31" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
         <v>127785435</v>
       </c>
       <c r="B32" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4097,7 +4097,7 @@
         <v>127784839</v>
       </c>
       <c r="B33" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4209,7 +4209,7 @@
         <v>127785662</v>
       </c>
       <c r="B34" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>127785113</v>
       </c>
       <c r="B35" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>127784998</v>
       </c>
       <c r="B36" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>127785496</v>
       </c>
       <c r="B37" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>127785128</v>
       </c>
       <c r="B38" t="n">
-        <v>105516</v>
+        <v>105609</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4773,7 +4773,7 @@
         <v>127785306</v>
       </c>
       <c r="B39" t="n">
-        <v>98478</v>
+        <v>98571</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY39"/>
+  <dimension ref="A1:AY50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4880,6 +4880,1093 @@
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>129705708</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>654795</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6648439</v>
+      </c>
+      <c r="S40" t="n">
+        <v>15</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>20 buketter</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>129705705</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>654807</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6648428</v>
+      </c>
+      <c r="S41" t="n">
+        <v>15</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>6 buketter</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>129705711</v>
+      </c>
+      <c r="B42" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>654795</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6648440</v>
+      </c>
+      <c r="S42" t="n">
+        <v>15</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>129705720</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92237</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1339</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Brandticka</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Pycnoporellus fulgens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Fr.) Donk</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>654706</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6648365</v>
+      </c>
+      <c r="S43" t="n">
+        <v>15</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>129705683</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97014</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>53</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>654786</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6648431</v>
+      </c>
+      <c r="S44" t="n">
+        <v>15</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>129705688</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>654694</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6648393</v>
+      </c>
+      <c r="S45" t="n">
+        <v>15</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>129705687</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57895</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>654760</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6648382</v>
+      </c>
+      <c r="S46" t="n">
+        <v>15</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>129705696</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57732</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>654802</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6648374</v>
+      </c>
+      <c r="S47" t="n">
+        <v>15</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>129705724</v>
+      </c>
+      <c r="B48" t="n">
+        <v>92240</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6031</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Blomkålssvamp</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Sparassis crispa</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>654713</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6648453</v>
+      </c>
+      <c r="S48" t="n">
+        <v>15</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>129705709</v>
+      </c>
+      <c r="B49" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>654738</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6648389</v>
+      </c>
+      <c r="S49" t="n">
+        <v>15</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>20 buketter</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>129705707</v>
+      </c>
+      <c r="B50" t="n">
+        <v>98768</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>654736</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6648386</v>
+      </c>
+      <c r="S50" t="n">
+        <v>15</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>30 buketter</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -4885,7 +4885,7 @@
         <v>129705708</v>
       </c>
       <c r="B40" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129705705</v>
+        <v>129705711</v>
       </c>
       <c r="B41" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654807</v>
+        <v>654795</v>
       </c>
       <c r="R41" t="n">
-        <v>6648428</v>
+        <v>6648440</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5055,11 +5055,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>6 buketter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5086,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129705711</v>
+        <v>129705705</v>
       </c>
       <c r="B42" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5121,10 +5116,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654795</v>
+        <v>654807</v>
       </c>
       <c r="R42" t="n">
-        <v>6648440</v>
+        <v>6648428</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5157,6 +5152,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>6 buketter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,7 +5186,7 @@
         <v>129705720</v>
       </c>
       <c r="B43" t="n">
-        <v>92237</v>
+        <v>92238</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>129705683</v>
       </c>
       <c r="B44" t="n">
-        <v>97014</v>
+        <v>97015</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>129705688</v>
       </c>
       <c r="B45" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>129705687</v>
       </c>
       <c r="B46" t="n">
-        <v>57895</v>
+        <v>57896</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>129705696</v>
       </c>
       <c r="B47" t="n">
-        <v>57732</v>
+        <v>57733</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>129705724</v>
       </c>
       <c r="B48" t="n">
-        <v>92240</v>
+        <v>92241</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>129705709</v>
       </c>
       <c r="B49" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>129705707</v>
       </c>
       <c r="B50" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -4885,7 +4885,7 @@
         <v>129705708</v>
       </c>
       <c r="B40" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129705711</v>
       </c>
       <c r="B41" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>129705705</v>
       </c>
       <c r="B42" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>129705720</v>
       </c>
       <c r="B43" t="n">
-        <v>92238</v>
+        <v>92243</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>129705683</v>
       </c>
       <c r="B44" t="n">
-        <v>97015</v>
+        <v>97020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>129705724</v>
       </c>
       <c r="B48" t="n">
-        <v>92241</v>
+        <v>92246</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>129705709</v>
       </c>
       <c r="B49" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>129705707</v>
       </c>
       <c r="B50" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -4885,7 +4885,7 @@
         <v>129705708</v>
       </c>
       <c r="B40" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129705711</v>
       </c>
       <c r="B41" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>129705705</v>
       </c>
       <c r="B42" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>129705720</v>
       </c>
       <c r="B43" t="n">
-        <v>92243</v>
+        <v>92247</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>129705683</v>
       </c>
       <c r="B44" t="n">
-        <v>97020</v>
+        <v>97024</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>129705724</v>
       </c>
       <c r="B48" t="n">
-        <v>92246</v>
+        <v>92250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>129705709</v>
       </c>
       <c r="B49" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>129705707</v>
       </c>
       <c r="B50" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -4885,7 +4885,7 @@
         <v>129705708</v>
       </c>
       <c r="B40" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129705711</v>
       </c>
       <c r="B41" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>129705705</v>
       </c>
       <c r="B42" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>129705720</v>
       </c>
       <c r="B43" t="n">
-        <v>92247</v>
+        <v>92249</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>129705683</v>
       </c>
       <c r="B44" t="n">
-        <v>97024</v>
+        <v>97026</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>129705724</v>
       </c>
       <c r="B48" t="n">
-        <v>92250</v>
+        <v>92252</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>129705709</v>
       </c>
       <c r="B49" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>129705707</v>
       </c>
       <c r="B50" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -4885,7 +4885,7 @@
         <v>129705708</v>
       </c>
       <c r="B40" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129705711</v>
       </c>
       <c r="B41" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>129705705</v>
       </c>
       <c r="B42" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>129705683</v>
       </c>
       <c r="B44" t="n">
-        <v>97026</v>
+        <v>97036</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>129705709</v>
       </c>
       <c r="B49" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>129705707</v>
       </c>
       <c r="B50" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -4885,7 +4885,7 @@
         <v>129705708</v>
       </c>
       <c r="B40" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129705711</v>
       </c>
       <c r="B41" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>129705705</v>
       </c>
       <c r="B42" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>129705720</v>
       </c>
       <c r="B43" t="n">
-        <v>92249</v>
+        <v>92252</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>129705683</v>
       </c>
       <c r="B44" t="n">
-        <v>97036</v>
+        <v>97040</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>129705688</v>
       </c>
       <c r="B45" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>129705687</v>
       </c>
       <c r="B46" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>129705696</v>
       </c>
       <c r="B47" t="n">
-        <v>57733</v>
+        <v>57734</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>129705724</v>
       </c>
       <c r="B48" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>129705709</v>
       </c>
       <c r="B49" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>129705707</v>
       </c>
       <c r="B50" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -4885,7 +4885,7 @@
         <v>129705708</v>
       </c>
       <c r="B40" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4987,7 +4987,7 @@
         <v>129705711</v>
       </c>
       <c r="B41" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5084,7 +5084,7 @@
         <v>129705705</v>
       </c>
       <c r="B42" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>129705720</v>
       </c>
       <c r="B43" t="n">
-        <v>92252</v>
+        <v>92255</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>129705683</v>
       </c>
       <c r="B44" t="n">
-        <v>97040</v>
+        <v>97043</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>129705688</v>
       </c>
       <c r="B45" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>129705687</v>
       </c>
       <c r="B46" t="n">
-        <v>57895</v>
+        <v>57898</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5574,7 +5574,7 @@
         <v>129705696</v>
       </c>
       <c r="B47" t="n">
-        <v>57734</v>
+        <v>57737</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>129705724</v>
       </c>
       <c r="B48" t="n">
-        <v>92255</v>
+        <v>92258</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>129705709</v>
       </c>
       <c r="B49" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>129705707</v>
       </c>
       <c r="B50" t="n">
-        <v>98794</v>
+        <v>98797</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -4885,7 +4885,7 @@
         <v>129705708</v>
       </c>
       <c r="B40" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129705711</v>
+        <v>129705705</v>
       </c>
       <c r="B41" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654795</v>
+        <v>654807</v>
       </c>
       <c r="R41" t="n">
-        <v>6648440</v>
+        <v>6648428</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5055,6 +5055,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>6 buketter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5081,10 +5086,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129705705</v>
+        <v>129705711</v>
       </c>
       <c r="B42" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5116,10 +5121,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654807</v>
+        <v>654795</v>
       </c>
       <c r="R42" t="n">
-        <v>6648428</v>
+        <v>6648440</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5152,11 +5157,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>6 buketter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,7 +5186,7 @@
         <v>129705720</v>
       </c>
       <c r="B43" t="n">
-        <v>92255</v>
+        <v>92256</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>129705683</v>
       </c>
       <c r="B44" t="n">
-        <v>97043</v>
+        <v>97044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>129705724</v>
       </c>
       <c r="B48" t="n">
-        <v>92258</v>
+        <v>92259</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>129705709</v>
       </c>
       <c r="B49" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>129705707</v>
       </c>
       <c r="B50" t="n">
-        <v>98797</v>
+        <v>98798</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -4885,7 +4885,7 @@
         <v>129705708</v>
       </c>
       <c r="B40" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4984,10 +4984,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129705705</v>
+        <v>129705711</v>
       </c>
       <c r="B41" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5019,10 +5019,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654807</v>
+        <v>654795</v>
       </c>
       <c r="R41" t="n">
-        <v>6648428</v>
+        <v>6648440</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -5055,11 +5055,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>6 buketter</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5086,10 +5081,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129705711</v>
+        <v>129705705</v>
       </c>
       <c r="B42" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5121,10 +5116,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654795</v>
+        <v>654807</v>
       </c>
       <c r="R42" t="n">
-        <v>6648440</v>
+        <v>6648428</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -5157,6 +5152,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>6 buketter</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5186,7 +5186,7 @@
         <v>129705720</v>
       </c>
       <c r="B43" t="n">
-        <v>92256</v>
+        <v>92273</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5283,7 +5283,7 @@
         <v>129705683</v>
       </c>
       <c r="B44" t="n">
-        <v>97044</v>
+        <v>97061</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5380,7 +5380,7 @@
         <v>129705688</v>
       </c>
       <c r="B45" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5477,7 +5477,7 @@
         <v>129705687</v>
       </c>
       <c r="B46" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
         <v>129705724</v>
       </c>
       <c r="B48" t="n">
-        <v>92259</v>
+        <v>92276</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>129705709</v>
       </c>
       <c r="B49" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5870,7 +5870,7 @@
         <v>129705707</v>
       </c>
       <c r="B50" t="n">
-        <v>98798</v>
+        <v>98815</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -797,7 +797,7 @@
         <v>127053045</v>
       </c>
       <c r="B3" t="n">
-        <v>96708</v>
+        <v>96689</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>127053050</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>127053055</v>
       </c>
       <c r="B5" t="n">
-        <v>100638</v>
+        <v>100618</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
         <v>127053046</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>96689</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1211,7 +1211,7 @@
         <v>127053054</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>98436</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,45 +1305,57 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127053052</v>
+        <v>127053047</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>96689</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654680</v>
+        <v>654771</v>
       </c>
       <c r="R8" t="n">
-        <v>6648398</v>
+        <v>6648423</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,6 +1396,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,57 +1415,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127053047</v>
+        <v>127053052</v>
       </c>
       <c r="B9" t="n">
-        <v>96708</v>
+        <v>98436</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654771</v>
+        <v>654680</v>
       </c>
       <c r="R9" t="n">
-        <v>6648423</v>
+        <v>6648398</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1493,7 +1494,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1512,10 +1512,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127053051</v>
+        <v>127053049</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>92047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1523,21 +1523,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,10 +1547,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654708</v>
+        <v>654713</v>
       </c>
       <c r="R10" t="n">
-        <v>6648411</v>
+        <v>6648417</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1609,10 +1609,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127053049</v>
+        <v>127053051</v>
       </c>
       <c r="B11" t="n">
-        <v>92066</v>
+        <v>98436</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1620,21 +1620,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1105</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1644,10 +1644,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654713</v>
+        <v>654708</v>
       </c>
       <c r="R11" t="n">
-        <v>6648417</v>
+        <v>6648411</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1709,7 +1709,7 @@
         <v>127126027</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>127125643</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1941,7 +1941,7 @@
         <v>127126120</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>127126282</v>
       </c>
       <c r="B15" t="n">
-        <v>96719</v>
+        <v>96689</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>127125022</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>127125124</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>5196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>127125864</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>127125059</v>
       </c>
       <c r="B19" t="n">
-        <v>98384</v>
+        <v>98353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2624,7 +2624,7 @@
         <v>127126407</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>127124755</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>127125737</v>
       </c>
       <c r="B22" t="n">
-        <v>5197</v>
+        <v>5196</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,38 +2965,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127123843</v>
+        <v>127124848</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>8447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,13 +3005,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654639</v>
+        <v>654727</v>
       </c>
       <c r="R23" t="n">
-        <v>6648349</v>
+        <v>6648365</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,7 +3040,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,38 +3077,38 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127124848</v>
+        <v>127123843</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>57654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,13 +3117,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654727</v>
+        <v>654639</v>
       </c>
       <c r="R24" t="n">
-        <v>6648365</v>
+        <v>6648349</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3192,7 +3192,7 @@
         <v>127125758</v>
       </c>
       <c r="B25" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3304,7 +3304,7 @@
         <v>127124825</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>127123881</v>
       </c>
       <c r="B27" t="n">
-        <v>43942</v>
+        <v>43935</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>127124644</v>
       </c>
       <c r="B28" t="n">
-        <v>5197</v>
+        <v>5196</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3644,7 +3644,7 @@
         <v>127124616</v>
       </c>
       <c r="B29" t="n">
-        <v>5177</v>
+        <v>5176</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -5972,7 +5972,7 @@
         <v>131735004</v>
       </c>
       <c r="B51" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6082,7 +6082,7 @@
         <v>131734998</v>
       </c>
       <c r="B52" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6189,10 +6189,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131735005</v>
+        <v>131734971</v>
       </c>
       <c r="B53" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654755</v>
+        <v>654769</v>
       </c>
       <c r="R53" t="n">
-        <v>6648433</v>
+        <v>6648414</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6268,7 +6268,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6299,10 +6299,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131734971</v>
+        <v>131734972</v>
       </c>
       <c r="B54" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654769</v>
+        <v>654752</v>
       </c>
       <c r="R54" t="n">
-        <v>6648414</v>
+        <v>6648405</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6409,10 +6409,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131734972</v>
+        <v>131735005</v>
       </c>
       <c r="B55" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654752</v>
+        <v>654755</v>
       </c>
       <c r="R55" t="n">
-        <v>6648405</v>
+        <v>6648433</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6519,10 +6519,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131734953</v>
+        <v>131734974</v>
       </c>
       <c r="B56" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6549,7 +6549,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6558,10 +6558,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654765</v>
+        <v>654744</v>
       </c>
       <c r="R56" t="n">
-        <v>6648472</v>
+        <v>6648398</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6598,7 +6598,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6629,10 +6629,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131734966</v>
+        <v>131734953</v>
       </c>
       <c r="B57" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6659,7 +6659,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6668,10 +6668,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654763</v>
+        <v>654765</v>
       </c>
       <c r="R57" t="n">
-        <v>6648431</v>
+        <v>6648472</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6739,10 +6739,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131734974</v>
+        <v>131735000</v>
       </c>
       <c r="B58" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6778,10 +6778,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654744</v>
+        <v>654772</v>
       </c>
       <c r="R58" t="n">
-        <v>6648398</v>
+        <v>6648435</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6852,7 +6852,7 @@
         <v>131734995</v>
       </c>
       <c r="B59" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6959,10 +6959,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131735000</v>
+        <v>131734966</v>
       </c>
       <c r="B60" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,7 +6989,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6998,10 +6998,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654772</v>
+        <v>654763</v>
       </c>
       <c r="R60" t="n">
-        <v>6648435</v>
+        <v>6648431</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7069,10 +7069,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131734961</v>
+        <v>131734969</v>
       </c>
       <c r="B61" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7108,10 +7108,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654791</v>
+        <v>654769</v>
       </c>
       <c r="R61" t="n">
-        <v>6648444</v>
+        <v>6648419</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7148,7 +7148,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7179,10 +7179,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131734969</v>
+        <v>131734961</v>
       </c>
       <c r="B62" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7209,7 +7209,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7218,10 +7218,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654769</v>
+        <v>654791</v>
       </c>
       <c r="R62" t="n">
-        <v>6648419</v>
+        <v>6648444</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7258,7 +7258,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7292,7 +7292,7 @@
         <v>131735011</v>
       </c>
       <c r="B63" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7402,7 +7402,7 @@
         <v>131734976</v>
       </c>
       <c r="B64" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>131735008</v>
       </c>
       <c r="B65" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>131734978</v>
       </c>
       <c r="B66" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7729,10 +7729,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131734990</v>
+        <v>131734973</v>
       </c>
       <c r="B67" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7759,7 +7759,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7768,10 +7768,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654759</v>
+        <v>654745</v>
       </c>
       <c r="R67" t="n">
-        <v>6648451</v>
+        <v>6648400</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7808,7 +7808,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7839,10 +7839,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131734973</v>
+        <v>131734996</v>
       </c>
       <c r="B68" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7878,10 +7878,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654745</v>
+        <v>654792</v>
       </c>
       <c r="R68" t="n">
-        <v>6648400</v>
+        <v>6648440</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7949,10 +7949,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131734996</v>
+        <v>131734990</v>
       </c>
       <c r="B69" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7988,10 +7988,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654792</v>
+        <v>654759</v>
       </c>
       <c r="R69" t="n">
-        <v>6648440</v>
+        <v>6648451</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8059,10 +8059,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131735006</v>
+        <v>131734989</v>
       </c>
       <c r="B70" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8089,19 +8089,19 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Björkhagen Öst, Upl</t>
+          <t>Björkhagen Nordost, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>654741</v>
+        <v>654712</v>
       </c>
       <c r="R70" t="n">
-        <v>6648426</v>
+        <v>6648455</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8169,10 +8169,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131734989</v>
+        <v>131734958</v>
       </c>
       <c r="B71" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8199,16 +8199,16 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Björkhagen Nordost, Upl</t>
+          <t>Björkhagen Öst, Upl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>654712</v>
+        <v>654774</v>
       </c>
       <c r="R71" t="n">
         <v>6648455</v>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8279,10 +8279,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131734962</v>
+        <v>131735006</v>
       </c>
       <c r="B72" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8318,10 +8318,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>654787</v>
+        <v>654741</v>
       </c>
       <c r="R72" t="n">
-        <v>6648429</v>
+        <v>6648426</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8392,7 +8392,7 @@
         <v>131734979</v>
       </c>
       <c r="B73" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8499,10 +8499,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131734958</v>
+        <v>131734962</v>
       </c>
       <c r="B74" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
@@ -8538,10 +8538,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>654774</v>
+        <v>654787</v>
       </c>
       <c r="R74" t="n">
-        <v>6648455</v>
+        <v>6648429</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8578,7 +8578,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8609,10 +8609,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131734967</v>
+        <v>131735003</v>
       </c>
       <c r="B75" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8648,10 +8648,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>654767</v>
+        <v>654763</v>
       </c>
       <c r="R75" t="n">
-        <v>6648426</v>
+        <v>6648432</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8719,10 +8719,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131735003</v>
+        <v>131734967</v>
       </c>
       <c r="B76" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8758,10 +8758,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>654763</v>
+        <v>654767</v>
       </c>
       <c r="R76" t="n">
-        <v>6648432</v>
+        <v>6648426</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8829,10 +8829,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131734965</v>
+        <v>131734981</v>
       </c>
       <c r="B77" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8859,7 +8859,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8868,10 +8868,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>654766</v>
+        <v>654730</v>
       </c>
       <c r="R77" t="n">
-        <v>6648439</v>
+        <v>6648387</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8908,7 +8908,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8939,10 +8939,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131734981</v>
+        <v>131734965</v>
       </c>
       <c r="B78" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8969,7 +8969,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8978,10 +8978,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>654730</v>
+        <v>654766</v>
       </c>
       <c r="R78" t="n">
-        <v>6648387</v>
+        <v>6648439</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9018,7 +9018,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9052,7 +9052,7 @@
         <v>131735010</v>
       </c>
       <c r="B79" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9159,10 +9159,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131734982</v>
+        <v>131735009</v>
       </c>
       <c r="B80" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9198,10 +9198,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>654725</v>
+        <v>654752</v>
       </c>
       <c r="R80" t="n">
-        <v>6648393</v>
+        <v>6648398</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9272,7 +9272,7 @@
         <v>131734956</v>
       </c>
       <c r="B81" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>131735013</v>
       </c>
       <c r="B82" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9489,10 +9489,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131735009</v>
+        <v>131734993</v>
       </c>
       <c r="B83" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9528,10 +9528,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>654752</v>
+        <v>654772</v>
       </c>
       <c r="R83" t="n">
-        <v>6648398</v>
+        <v>6648449</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9599,10 +9599,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131734993</v>
+        <v>131734982</v>
       </c>
       <c r="B84" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9638,10 +9638,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>654772</v>
+        <v>654725</v>
       </c>
       <c r="R84" t="n">
-        <v>6648449</v>
+        <v>6648393</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9709,10 +9709,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131734968</v>
+        <v>131735002</v>
       </c>
       <c r="B85" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -9748,10 +9748,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654757</v>
+        <v>654764</v>
       </c>
       <c r="R85" t="n">
-        <v>6648426</v>
+        <v>6648424</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9788,7 +9788,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9819,10 +9819,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131735002</v>
+        <v>131734968</v>
       </c>
       <c r="B86" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9849,7 +9849,7 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -9858,10 +9858,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654764</v>
+        <v>654757</v>
       </c>
       <c r="R86" t="n">
-        <v>6648424</v>
+        <v>6648426</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9898,7 +9898,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9929,10 +9929,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131734977</v>
+        <v>131734960</v>
       </c>
       <c r="B87" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
@@ -9968,10 +9968,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>654741</v>
+        <v>654792</v>
       </c>
       <c r="R87" t="n">
-        <v>6648385</v>
+        <v>6648447</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10008,7 +10008,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10039,10 +10039,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131734960</v>
+        <v>131734954</v>
       </c>
       <c r="B88" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10069,7 +10069,7 @@
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10078,10 +10078,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>654792</v>
+        <v>654763</v>
       </c>
       <c r="R88" t="n">
-        <v>6648447</v>
+        <v>6648468</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10149,10 +10149,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131734988</v>
+        <v>131734977</v>
       </c>
       <c r="B89" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10184,14 +10184,14 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Björkhagen Nordost, Upl</t>
+          <t>Björkhagen Öst, Upl</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>654715</v>
+        <v>654741</v>
       </c>
       <c r="R89" t="n">
-        <v>6648463</v>
+        <v>6648385</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10259,10 +10259,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131734954</v>
+        <v>131734991</v>
       </c>
       <c r="B90" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -10298,10 +10298,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>654763</v>
+        <v>654767</v>
       </c>
       <c r="R90" t="n">
-        <v>6648468</v>
+        <v>6648447</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10338,7 +10338,7 @@
       </c>
       <c r="AC90" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10369,10 +10369,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131734991</v>
+        <v>131734988</v>
       </c>
       <c r="B91" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10399,19 +10399,19 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Björkhagen Öst, Upl</t>
+          <t>Björkhagen Nordost, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>654767</v>
+        <v>654715</v>
       </c>
       <c r="R91" t="n">
-        <v>6648446</v>
+        <v>6648463</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10448,7 +10448,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10482,7 +10482,7 @@
         <v>131735001</v>
       </c>
       <c r="B92" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10592,7 +10592,7 @@
         <v>131734964</v>
       </c>
       <c r="B93" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10702,7 +10702,7 @@
         <v>131734984</v>
       </c>
       <c r="B94" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10809,10 +10809,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131735007</v>
+        <v>131735017</v>
       </c>
       <c r="B95" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>156</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10848,10 +10848,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>654747</v>
+        <v>654780</v>
       </c>
       <c r="R95" t="n">
-        <v>6648424</v>
+        <v>6648423</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10919,10 +10919,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131735017</v>
+        <v>131735007</v>
       </c>
       <c r="B96" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10949,7 +10949,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10958,10 +10958,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>654780</v>
+        <v>654747</v>
       </c>
       <c r="R96" t="n">
-        <v>6648423</v>
+        <v>6648424</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11032,7 +11032,7 @@
         <v>131734999</v>
       </c>
       <c r="B97" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11142,7 +11142,7 @@
         <v>131734985</v>
       </c>
       <c r="B98" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>131734975</v>
       </c>
       <c r="B99" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>131734997</v>
       </c>
       <c r="B100" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>131734970</v>
       </c>
       <c r="B101" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>131734959</v>
       </c>
       <c r="B102" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11692,7 +11692,7 @@
         <v>131734983</v>
       </c>
       <c r="B103" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11799,10 +11799,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131734963</v>
+        <v>131734980</v>
       </c>
       <c r="B104" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11829,7 +11829,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11838,10 +11838,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>654787</v>
+        <v>654730</v>
       </c>
       <c r="R104" t="n">
-        <v>6648437</v>
+        <v>6648380</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11909,10 +11909,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131734986</v>
+        <v>131734963</v>
       </c>
       <c r="B105" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11939,19 +11939,19 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Björkhagen Nordost, Upl</t>
+          <t>Björkhagen Öst, Upl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>654694</v>
+        <v>654787</v>
       </c>
       <c r="R105" t="n">
-        <v>6648453</v>
+        <v>6648437</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11988,7 +11988,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12022,7 +12022,7 @@
         <v>131735012</v>
       </c>
       <c r="B106" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12129,10 +12129,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131734980</v>
+        <v>131734986</v>
       </c>
       <c r="B107" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12159,19 +12159,19 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Björkhagen Öst, Upl</t>
+          <t>Björkhagen Nordost, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>654730</v>
+        <v>654694</v>
       </c>
       <c r="R107" t="n">
-        <v>6648380</v>
+        <v>6648453</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12242,7 +12242,7 @@
         <v>131734987</v>
       </c>
       <c r="B108" t="n">
-        <v>99095</v>
+        <v>99098</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -6189,7 +6189,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131734971</v>
+        <v>131734972</v>
       </c>
       <c r="B53" t="n">
         <v>99098</v>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654769</v>
+        <v>654752</v>
       </c>
       <c r="R53" t="n">
-        <v>6648414</v>
+        <v>6648405</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6299,7 +6299,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131734972</v>
+        <v>131735005</v>
       </c>
       <c r="B54" t="n">
         <v>99098</v>
@@ -6329,7 +6329,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6338,10 +6338,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654752</v>
+        <v>654755</v>
       </c>
       <c r="R54" t="n">
-        <v>6648405</v>
+        <v>6648433</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6378,7 +6378,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6409,7 +6409,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131735005</v>
+        <v>131734971</v>
       </c>
       <c r="B55" t="n">
         <v>99098</v>
@@ -6439,7 +6439,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6448,10 +6448,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654755</v>
+        <v>654769</v>
       </c>
       <c r="R55" t="n">
-        <v>6648433</v>
+        <v>6648414</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,7 +6488,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -10809,7 +10809,7 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131735017</v>
+        <v>131735007</v>
       </c>
       <c r="B95" t="n">
         <v>99098</v>
@@ -10839,7 +10839,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10848,10 +10848,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>654780</v>
+        <v>654747</v>
       </c>
       <c r="R95" t="n">
-        <v>6648423</v>
+        <v>6648424</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10888,7 +10888,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10919,7 +10919,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131735007</v>
+        <v>131734999</v>
       </c>
       <c r="B96" t="n">
         <v>99098</v>
@@ -10949,7 +10949,7 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P96" t="inlineStr">
@@ -10958,10 +10958,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>654747</v>
+        <v>654777</v>
       </c>
       <c r="R96" t="n">
-        <v>6648424</v>
+        <v>6648431</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10998,7 +10998,7 @@
       </c>
       <c r="AC96" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11029,7 +11029,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131734999</v>
+        <v>131735017</v>
       </c>
       <c r="B97" t="n">
         <v>99098</v>
@@ -11059,7 +11059,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>156</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11068,10 +11068,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>654777</v>
+        <v>654780</v>
       </c>
       <c r="R97" t="n">
-        <v>6648431</v>
+        <v>6648423</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11108,7 +11108,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>156</t>
         </is>
       </c>
       <c r="AD97" t="b">

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -9049,7 +9049,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131735010</v>
+        <v>131734993</v>
       </c>
       <c r="B79" t="n">
         <v>99098</v>
@@ -9079,7 +9079,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9088,10 +9088,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>654751</v>
+        <v>654772</v>
       </c>
       <c r="R79" t="n">
-        <v>6648394</v>
+        <v>6648449</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9128,7 +9128,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9159,7 +9159,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131735009</v>
+        <v>131734982</v>
       </c>
       <c r="B80" t="n">
         <v>99098</v>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9198,10 +9198,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>654752</v>
+        <v>654725</v>
       </c>
       <c r="R80" t="n">
-        <v>6648398</v>
+        <v>6648393</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9269,7 +9269,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131734956</v>
+        <v>131735010</v>
       </c>
       <c r="B81" t="n">
         <v>99098</v>
@@ -9299,7 +9299,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9308,10 +9308,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>654762</v>
+        <v>654751</v>
       </c>
       <c r="R81" t="n">
-        <v>6648462</v>
+        <v>6648394</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9379,7 +9379,7 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131735013</v>
+        <v>131735009</v>
       </c>
       <c r="B82" t="n">
         <v>99098</v>
@@ -9409,19 +9409,19 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Björkhagen Nordost, Upl</t>
+          <t>Björkhagen Öst, Upl</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>654673</v>
+        <v>654752</v>
       </c>
       <c r="R82" t="n">
-        <v>6648408</v>
+        <v>6648398</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9489,7 +9489,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131734993</v>
+        <v>131734956</v>
       </c>
       <c r="B83" t="n">
         <v>99098</v>
@@ -9519,7 +9519,7 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
@@ -9528,10 +9528,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>654772</v>
+        <v>654762</v>
       </c>
       <c r="R83" t="n">
-        <v>6648449</v>
+        <v>6648462</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9568,7 +9568,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9599,7 +9599,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131734982</v>
+        <v>131735013</v>
       </c>
       <c r="B84" t="n">
         <v>99098</v>
@@ -9629,19 +9629,19 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Björkhagen Öst, Upl</t>
+          <t>Björkhagen Nordost, Upl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>654725</v>
+        <v>654673</v>
       </c>
       <c r="R84" t="n">
-        <v>6648393</v>
+        <v>6648408</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9678,7 +9678,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -11249,7 +11249,7 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131734975</v>
+        <v>131734970</v>
       </c>
       <c r="B99" t="n">
         <v>99098</v>
@@ -11279,7 +11279,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11288,10 +11288,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>654745</v>
+        <v>654768</v>
       </c>
       <c r="R99" t="n">
-        <v>6648398</v>
+        <v>6648417</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11328,7 +11328,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11359,7 +11359,7 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131734997</v>
+        <v>131734975</v>
       </c>
       <c r="B100" t="n">
         <v>99098</v>
@@ -11389,7 +11389,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11398,10 +11398,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>654786</v>
+        <v>654745</v>
       </c>
       <c r="R100" t="n">
-        <v>6648440</v>
+        <v>6648398</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11438,7 +11438,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11469,7 +11469,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131734970</v>
+        <v>131734997</v>
       </c>
       <c r="B101" t="n">
         <v>99098</v>
@@ -11508,10 +11508,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>654768</v>
+        <v>654786</v>
       </c>
       <c r="R101" t="n">
-        <v>6648417</v>
+        <v>6648440</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11799,7 +11799,7 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131734980</v>
+        <v>131734986</v>
       </c>
       <c r="B104" t="n">
         <v>99098</v>
@@ -11829,19 +11829,19 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Björkhagen Öst, Upl</t>
+          <t>Björkhagen Nordost, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>654730</v>
+        <v>654694</v>
       </c>
       <c r="R104" t="n">
-        <v>6648380</v>
+        <v>6648453</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11878,7 +11878,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12129,7 +12129,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131734986</v>
+        <v>131734980</v>
       </c>
       <c r="B107" t="n">
         <v>99098</v>
@@ -12159,19 +12159,19 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Björkhagen Nordost, Upl</t>
+          <t>Björkhagen Öst, Upl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>654694</v>
+        <v>654730</v>
       </c>
       <c r="R107" t="n">
-        <v>6648453</v>
+        <v>6648380</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD107" t="b">

--- a/artfynd/A 25609-2025 artfynd.xlsx
+++ b/artfynd/A 25609-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY108"/>
+  <dimension ref="A1:AY118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,52 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>77318200</v>
+        <v>127053045</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tomta, 1,5 km SV-ut, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>654529.893645844</v>
+        <v>654789</v>
       </c>
       <c r="R2" t="n">
-        <v>6648283.201259622</v>
+        <v>6648453</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,22 +752,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2019-04-21</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,26 +773,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström, Thorleif Joelson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127053045</v>
+        <v>127053046</v>
       </c>
       <c r="B3" t="n">
-        <v>96708</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -824,7 +815,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>500</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>654789</v>
+        <v>654792</v>
       </c>
       <c r="R3" t="n">
-        <v>6648453</v>
+        <v>6648438</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,45 +895,57 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127053050</v>
+        <v>127053047</v>
       </c>
       <c r="B4" t="n">
-        <v>98456</v>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>cm²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>654722</v>
+        <v>654771</v>
       </c>
       <c r="R4" t="n">
-        <v>6648435</v>
+        <v>6648423</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -983,6 +986,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1001,48 +1005,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127053055</v>
+        <v>127126282</v>
       </c>
       <c r="B5" t="n">
-        <v>100638</v>
+        <v>97358</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>654681</v>
+        <v>654740</v>
       </c>
       <c r="R5" t="n">
-        <v>6648407</v>
+        <v>6648381</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1066,12 +1070,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,22 +1100,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127053046</v>
+        <v>129705683</v>
       </c>
       <c r="B6" t="n">
-        <v>96708</v>
+        <v>97358</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1126,32 +1140,20 @@
           <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>654792</v>
+        <v>654786</v>
       </c>
       <c r="R6" t="n">
-        <v>6648438</v>
+        <v>6648431</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1175,12 +1177,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,7 +1191,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1208,10 +1209,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127053054</v>
+        <v>127053049</v>
       </c>
       <c r="B7" t="n">
-        <v>98456</v>
+        <v>92662</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1219,21 +1220,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>1105</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1243,10 +1244,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>654699</v>
+        <v>654713</v>
       </c>
       <c r="R7" t="n">
-        <v>6648413</v>
+        <v>6648417</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,32 +1306,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127053052</v>
+        <v>129705720</v>
       </c>
       <c r="B8" t="n">
-        <v>98456</v>
+        <v>92564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1339</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brandticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pycnoporellus fulgens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Donk</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1340,13 +1341,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>654680</v>
+        <v>654706</v>
       </c>
       <c r="R8" t="n">
-        <v>6648398</v>
+        <v>6648365</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1370,12 +1371,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1402,57 +1403,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127053047</v>
+        <v>77516226</v>
       </c>
       <c r="B9" t="n">
-        <v>96708</v>
+        <v>92333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>53</v>
+        <v>4217</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>cm²</t>
-        </is>
-      </c>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Tomta, 1,3 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>654771</v>
+        <v>654826</v>
       </c>
       <c r="R9" t="n">
-        <v>6648423</v>
+        <v>6648329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,12 +1471,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1497,47 +1489,80 @@
       <c r="AG9" t="b">
         <v>0</v>
       </c>
-      <c r="AT9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>vanlig tall</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris var. sylvestris</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127053051</v>
+        <v>129705724</v>
       </c>
       <c r="B10" t="n">
-        <v>98456</v>
+        <v>92567</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1547,13 +1572,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>654708</v>
+        <v>654713</v>
       </c>
       <c r="R10" t="n">
-        <v>6648411</v>
+        <v>6648453</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1577,12 +1602,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1609,48 +1634,53 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127053049</v>
+        <v>127123843</v>
       </c>
       <c r="B11" t="n">
-        <v>92066</v>
+        <v>57950</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1105</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>654713</v>
+        <v>654639</v>
       </c>
       <c r="R11" t="n">
-        <v>6648417</v>
+        <v>6648349</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1674,12 +1704,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1694,54 +1734,50 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127126027</v>
+        <v>127125758</v>
       </c>
       <c r="B12" t="n">
-        <v>98467</v>
+        <v>57950</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1750,13 +1786,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>654747</v>
+        <v>654709</v>
       </c>
       <c r="R12" t="n">
-        <v>6648354</v>
+        <v>6648286</v>
       </c>
       <c r="S12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1822,57 +1858,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127125643</v>
+        <v>129705696</v>
       </c>
       <c r="B13" t="n">
-        <v>98467</v>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>654705</v>
+        <v>654802</v>
       </c>
       <c r="R13" t="n">
-        <v>6648385</v>
+        <v>6648374</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1896,22 +1923,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1926,69 +1943,69 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127126120</v>
+        <v>77318870</v>
       </c>
       <c r="B14" t="n">
-        <v>98467</v>
+        <v>4775</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, 1,5 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>654740</v>
+        <v>654532</v>
       </c>
       <c r="R14" t="n">
-        <v>6648381</v>
+        <v>6648253</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2012,22 +2029,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,66 +2043,100 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127126282</v>
+        <v>77318872</v>
       </c>
       <c r="B15" t="n">
-        <v>96719</v>
+        <v>5179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, 1,5 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>654740</v>
+        <v>654532</v>
       </c>
       <c r="R15" t="n">
-        <v>6648381</v>
+        <v>6648253</v>
       </c>
       <c r="S15" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2119,22 +2160,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2019-04-21</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2143,60 +2174,81 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127125022</v>
+        <v>127124616</v>
       </c>
       <c r="B16" t="n">
-        <v>98467</v>
+        <v>5179</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2205,13 +2257,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>654738</v>
+        <v>654640</v>
       </c>
       <c r="R16" t="n">
-        <v>6648375</v>
+        <v>6648354</v>
       </c>
       <c r="S16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2240,7 +2292,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2250,7 +2302,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2277,10 +2329,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127125124</v>
+        <v>127123881</v>
       </c>
       <c r="B17" t="n">
-        <v>5197</v>
+        <v>44177</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2288,27 +2340,27 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>105930</v>
+        <v>101735</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2317,13 +2369,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>654705</v>
+        <v>654640</v>
       </c>
       <c r="R17" t="n">
-        <v>6648385</v>
+        <v>6648354</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2352,7 +2404,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2362,7 +2414,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2389,57 +2441,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127125864</v>
+        <v>129705687</v>
       </c>
       <c r="B18" t="n">
-        <v>98467</v>
+        <v>58114</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>654709</v>
+        <v>654760</v>
       </c>
       <c r="R18" t="n">
-        <v>6648286</v>
+        <v>6648382</v>
       </c>
       <c r="S18" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2463,22 +2506,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2493,69 +2526,60 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127125059</v>
+        <v>129705688</v>
       </c>
       <c r="B19" t="n">
-        <v>98384</v>
+        <v>58114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>654738</v>
+        <v>654694</v>
       </c>
       <c r="R19" t="n">
-        <v>6648375</v>
+        <v>6648393</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,22 +2603,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,54 +2623,50 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127126407</v>
+        <v>127124644</v>
       </c>
       <c r="B20" t="n">
-        <v>98467</v>
+        <v>5199</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2665,13 +2675,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>654783</v>
+        <v>654725</v>
       </c>
       <c r="R20" t="n">
-        <v>6648421</v>
+        <v>6648334</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2700,7 +2710,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2710,7 +2720,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:24</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2737,42 +2747,38 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127124755</v>
+        <v>127125124</v>
       </c>
       <c r="B21" t="n">
-        <v>98467</v>
+        <v>5199</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>105930</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Semanotus undatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2781,13 +2787,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>654725</v>
+        <v>654705</v>
       </c>
       <c r="R21" t="n">
-        <v>6648334</v>
+        <v>6648385</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2816,7 +2822,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2826,7 +2832,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:10</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2856,7 +2862,7 @@
         <v>127125737</v>
       </c>
       <c r="B22" t="n">
-        <v>5197</v>
+        <v>5199</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2965,38 +2971,38 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127123843</v>
+        <v>127124848</v>
       </c>
       <c r="B23" t="n">
-        <v>57669</v>
+        <v>8455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -3005,13 +3011,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>654639</v>
+        <v>654727</v>
       </c>
       <c r="R23" t="n">
-        <v>6648349</v>
+        <v>6648365</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3040,7 +3046,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3050,7 +3056,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3077,10 +3083,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127124848</v>
+        <v>127125059</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>99035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3088,27 +3094,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>219790</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3117,13 +3127,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>654727</v>
+        <v>654738</v>
       </c>
       <c r="R24" t="n">
-        <v>6648365</v>
+        <v>6648375</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3189,53 +3199,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127125758</v>
+        <v>127053050</v>
       </c>
       <c r="B25" t="n">
-        <v>57669</v>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>654709</v>
+        <v>654722</v>
       </c>
       <c r="R25" t="n">
-        <v>6648286</v>
+        <v>6648435</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3259,22 +3264,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>13:24</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3289,22 +3284,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127124825</v>
+        <v>127053051</v>
       </c>
       <c r="B26" t="n">
-        <v>98467</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3329,29 +3324,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>654727</v>
+        <v>654708</v>
       </c>
       <c r="R26" t="n">
-        <v>6648365</v>
+        <v>6648411</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3375,22 +3361,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>13:10</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3405,62 +3381,57 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127123881</v>
+        <v>127053052</v>
       </c>
       <c r="B27" t="n">
-        <v>43942</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101735</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>654640</v>
+        <v>654680</v>
       </c>
       <c r="R27" t="n">
-        <v>6648354</v>
+        <v>6648398</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3487,22 +3458,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3517,62 +3478,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127124644</v>
+        <v>127053054</v>
       </c>
       <c r="B28" t="n">
-        <v>5197</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>105930</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Vintermossröret, Vintermossröret, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>654725</v>
+        <v>654699</v>
       </c>
       <c r="R28" t="n">
-        <v>6648334</v>
+        <v>6648413</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3599,22 +3555,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>12:28</t>
+          <t>2025-07-31</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3629,50 +3575,54 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Arvid de Jong</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127124616</v>
+        <v>127124755</v>
       </c>
       <c r="B29" t="n">
-        <v>5177</v>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3681,10 +3631,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>654640</v>
+        <v>654725</v>
       </c>
       <c r="R29" t="n">
-        <v>6648354</v>
+        <v>6648334</v>
       </c>
       <c r="S29" t="n">
         <v>4</v>
@@ -3716,7 +3666,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3726,7 +3676,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3753,10 +3703,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127785029</v>
+        <v>127124825</v>
       </c>
       <c r="B30" t="n">
-        <v>98571</v>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3781,25 +3731,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Tomta SV om, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>654805</v>
+        <v>654727</v>
       </c>
       <c r="R30" t="n">
-        <v>6648382</v>
+        <v>6648365</v>
       </c>
       <c r="S30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3823,27 +3777,22 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>20:08</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>20:08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Minst 50-talet bladrosetter.</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3858,22 +3807,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127785015</v>
+        <v>127125022</v>
       </c>
       <c r="B31" t="n">
-        <v>98571</v>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3898,25 +3847,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Tomta SV om, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>654819</v>
+        <v>654738</v>
       </c>
       <c r="R31" t="n">
-        <v>6648392</v>
+        <v>6648375</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3940,22 +3893,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>20:06</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3970,22 +3923,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127785435</v>
+        <v>127125643</v>
       </c>
       <c r="B32" t="n">
-        <v>98571</v>
+        <v>99118</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4010,25 +3963,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Tomta SV om, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>654700</v>
+        <v>654705</v>
       </c>
       <c r="R32" t="n">
-        <v>6648457</v>
+        <v>6648385</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4052,22 +4009,22 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>20:31</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4082,22 +4039,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127784839</v>
+        <v>127125864</v>
       </c>
       <c r="B33" t="n">
-        <v>98571</v>
+        <v>99118</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4122,25 +4079,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Tomta SV om, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>654838</v>
+        <v>654709</v>
       </c>
       <c r="R33" t="n">
-        <v>6648421</v>
+        <v>6648286</v>
       </c>
       <c r="S33" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4164,22 +4125,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>20:03</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4194,22 +4155,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127785662</v>
+        <v>127126027</v>
       </c>
       <c r="B34" t="n">
-        <v>98571</v>
+        <v>99118</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4234,25 +4195,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Tomta SV om, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>654746</v>
+        <v>654747</v>
       </c>
       <c r="R34" t="n">
-        <v>6648486</v>
+        <v>6648354</v>
       </c>
       <c r="S34" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4276,22 +4241,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>20:38</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4306,22 +4271,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127785113</v>
+        <v>127126120</v>
       </c>
       <c r="B35" t="n">
-        <v>98571</v>
+        <v>99118</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4346,25 +4311,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Tomta SV om, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>654803</v>
+        <v>654740</v>
       </c>
       <c r="R35" t="n">
-        <v>6648362</v>
+        <v>6648381</v>
       </c>
       <c r="S35" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4388,22 +4357,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4418,22 +4387,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127784998</v>
+        <v>127126407</v>
       </c>
       <c r="B36" t="n">
-        <v>98571</v>
+        <v>99118</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4458,22 +4427,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Tomta SV om, Upl</t>
+          <t>Vintermossröret, Vintermossröret, Upl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>654833</v>
+        <v>654783</v>
       </c>
       <c r="R36" t="n">
-        <v>6648417</v>
+        <v>6648421</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4500,22 +4473,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-08-24</t>
+          <t>2025-08-03</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>13:24</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4530,22 +4503,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anders Lindholm</t>
+          <t>Arvid de Jong</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127785496</v>
+        <v>127784814</v>
       </c>
       <c r="B37" t="n">
-        <v>98571</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4570,14 +4543,10 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="K37" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
@@ -4586,13 +4555,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>654725</v>
+        <v>654838</v>
       </c>
       <c r="R37" t="n">
-        <v>6648468</v>
+        <v>6648421</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4621,7 +4590,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4631,7 +4600,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4658,32 +4627,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127785128</v>
+        <v>127784998</v>
       </c>
       <c r="B38" t="n">
-        <v>105609</v>
+        <v>99118</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4698,13 +4667,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>654803</v>
+        <v>654833</v>
       </c>
       <c r="R38" t="n">
-        <v>6648362</v>
+        <v>6648417</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4733,7 +4702,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4743,7 +4712,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>20:12</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4770,10 +4739,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127785306</v>
+        <v>127785015</v>
       </c>
       <c r="B39" t="n">
-        <v>98571</v>
+        <v>99118</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4810,13 +4779,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>654761</v>
+        <v>654819</v>
       </c>
       <c r="R39" t="n">
-        <v>6648341</v>
+        <v>6648392</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4845,7 +4814,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4855,7 +4824,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:06</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4882,10 +4851,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129705708</v>
+        <v>127785029</v>
       </c>
       <c r="B40" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4911,19 +4880,24 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>654795</v>
+        <v>654805</v>
       </c>
       <c r="R40" t="n">
-        <v>6648439</v>
+        <v>6648382</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4947,17 +4921,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>20 buketter</t>
+          <t>Minst 50-talet bladrosetter.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4972,22 +4956,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129705711</v>
+        <v>127785113</v>
       </c>
       <c r="B41" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5013,19 +4997,24 @@
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>654795</v>
+        <v>654803</v>
       </c>
       <c r="R41" t="n">
-        <v>6648440</v>
+        <v>6648362</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5049,12 +5038,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>20:12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5069,22 +5068,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129705705</v>
+        <v>127785306</v>
       </c>
       <c r="B42" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5110,19 +5109,24 @@
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>654807</v>
+        <v>654761</v>
       </c>
       <c r="R42" t="n">
-        <v>6648428</v>
+        <v>6648341</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5146,17 +5150,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>6 buketter</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>20:22</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5171,57 +5180,62 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129705720</v>
+        <v>127785435</v>
       </c>
       <c r="B43" t="n">
-        <v>92278</v>
+        <v>99118</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1339</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brandticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Pycnoporellus fulgens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Donk</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>654706</v>
+        <v>654700</v>
       </c>
       <c r="R43" t="n">
-        <v>6648365</v>
+        <v>6648457</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5248,12 +5262,22 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>20:31</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5268,60 +5292,69 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129705683</v>
+        <v>127785496</v>
       </c>
       <c r="B44" t="n">
-        <v>97066</v>
+        <v>99118</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>654786</v>
+        <v>654725</v>
       </c>
       <c r="R44" t="n">
-        <v>6648431</v>
+        <v>6648468</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5345,12 +5378,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>20:32</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5365,60 +5408,65 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129705688</v>
+        <v>127785581</v>
       </c>
       <c r="B45" t="n">
-        <v>57899</v>
+        <v>99118</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>654694</v>
+        <v>654763</v>
       </c>
       <c r="R45" t="n">
-        <v>6648393</v>
+        <v>6648504</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5442,12 +5490,22 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5462,60 +5520,65 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129705687</v>
+        <v>127785662</v>
       </c>
       <c r="B46" t="n">
-        <v>57899</v>
+        <v>99118</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Tomta, Upl</t>
+          <t>Tomta SV om, Upl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>654760</v>
+        <v>654746</v>
       </c>
       <c r="R46" t="n">
-        <v>6648382</v>
+        <v>6648486</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5539,12 +5602,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-11-15</t>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>20:38</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5559,44 +5632,44 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Anders Lindholm</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129705696</v>
+        <v>129705705</v>
       </c>
       <c r="B47" t="n">
-        <v>57737</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5606,10 +5679,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>654802</v>
+        <v>654807</v>
       </c>
       <c r="R47" t="n">
-        <v>6648374</v>
+        <v>6648428</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5642,6 +5715,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>6 buketter</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5668,32 +5746,32 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129705724</v>
+        <v>129705707</v>
       </c>
       <c r="B48" t="n">
-        <v>92281</v>
+        <v>99118</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6031</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5703,10 +5781,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>654713</v>
+        <v>654736</v>
       </c>
       <c r="R48" t="n">
-        <v>6648453</v>
+        <v>6648386</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5739,6 +5817,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>30 buketter</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5765,10 +5848,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129705709</v>
+        <v>129705708</v>
       </c>
       <c r="B49" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5800,10 +5883,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>654738</v>
+        <v>654795</v>
       </c>
       <c r="R49" t="n">
-        <v>6648389</v>
+        <v>6648439</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5867,10 +5950,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129705707</v>
+        <v>129705709</v>
       </c>
       <c r="B50" t="n">
-        <v>98820</v>
+        <v>99118</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5902,10 +5985,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>654736</v>
+        <v>654738</v>
       </c>
       <c r="R50" t="n">
-        <v>6648386</v>
+        <v>6648389</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5942,7 +6025,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>30 buketter</t>
+          <t>20 buketter</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5969,10 +6052,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131735004</v>
+        <v>129705711</v>
       </c>
       <c r="B51" t="n">
-        <v>99098</v>
+        <v>99118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5997,24 +6080,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Björkhagen Öst, Upl</t>
+          <t>Tomta, Upl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>654763</v>
+        <v>654795</v>
       </c>
       <c r="R51" t="n">
-        <v>6648435</v>
+        <v>6648440</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6038,17 +6117,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>70</t>
+          <t>2025-11-15</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6063,26 +6137,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Helene Andersson</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Henrik Tykosson</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131734998</v>
+        <v>131734953</v>
       </c>
       <c r="B52" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6109,7 +6179,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6118,10 +6188,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>654784</v>
+        <v>654765</v>
       </c>
       <c r="R52" t="n">
-        <v>6648430</v>
+        <v>6648472</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6158,7 +6228,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6189,10 +6259,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131734972</v>
+        <v>131734954</v>
       </c>
       <c r="B53" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6219,7 +6289,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6228,10 +6298,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>654752</v>
+        <v>654763</v>
       </c>
       <c r="R53" t="n">
-        <v>6648405</v>
+        <v>6648468</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6268,7 +6338,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6299,10 +6369,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131735005</v>
+        <v>131734956</v>
       </c>
       <c r="B54" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6329,7 +6399,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6338,10 +6408,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>654755</v>
+        <v>654762</v>
       </c>
       <c r="R54" t="n">
-        <v>6648433</v>
+        <v>6648462</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6378,7 +6448,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6409,10 +6479,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131734971</v>
+        <v>131734957</v>
       </c>
       <c r="B55" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6439,7 +6509,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -6448,10 +6518,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>654769</v>
+        <v>654767</v>
       </c>
       <c r="R55" t="n">
-        <v>6648414</v>
+        <v>6648446</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6488,7 +6558,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6519,10 +6589,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131734974</v>
+        <v>131734958</v>
       </c>
       <c r="B56" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6558,10 +6628,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>654744</v>
+        <v>654774</v>
       </c>
       <c r="R56" t="n">
-        <v>6648398</v>
+        <v>6648455</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6629,10 +6699,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131734953</v>
+        <v>131734959</v>
       </c>
       <c r="B57" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6659,7 +6729,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -6668,10 +6738,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>654765</v>
+        <v>654781</v>
       </c>
       <c r="R57" t="n">
-        <v>6648472</v>
+        <v>6648448</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6708,7 +6778,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6739,10 +6809,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131735000</v>
+        <v>131734960</v>
       </c>
       <c r="B58" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6769,7 +6839,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -6778,10 +6848,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>654772</v>
+        <v>654792</v>
       </c>
       <c r="R58" t="n">
-        <v>6648435</v>
+        <v>6648447</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6818,7 +6888,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6849,10 +6919,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131734995</v>
+        <v>131734961</v>
       </c>
       <c r="B59" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6879,7 +6949,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -6888,10 +6958,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>654772</v>
+        <v>654791</v>
       </c>
       <c r="R59" t="n">
-        <v>6648453</v>
+        <v>6648444</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6928,7 +6998,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6959,10 +7029,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131734966</v>
+        <v>131734962</v>
       </c>
       <c r="B60" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6989,7 +7059,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -6998,10 +7068,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>654763</v>
+        <v>654787</v>
       </c>
       <c r="R60" t="n">
-        <v>6648431</v>
+        <v>6648429</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7038,7 +7108,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7069,10 +7139,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131734969</v>
+        <v>131734963</v>
       </c>
       <c r="B61" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7099,7 +7169,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7108,10 +7178,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>654769</v>
+        <v>654787</v>
       </c>
       <c r="R61" t="n">
-        <v>6648419</v>
+        <v>6648437</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7148,7 +7218,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7179,10 +7249,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131734961</v>
+        <v>131734964</v>
       </c>
       <c r="B62" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7209,7 +7279,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7218,10 +7288,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>654791</v>
+        <v>654772</v>
       </c>
       <c r="R62" t="n">
-        <v>6648444</v>
+        <v>6648442</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7258,7 +7328,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7289,10 +7359,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131735011</v>
+        <v>131734965</v>
       </c>
       <c r="B63" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7319,7 +7389,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7328,10 +7398,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>654749</v>
+        <v>654766</v>
       </c>
       <c r="R63" t="n">
-        <v>6648395</v>
+        <v>6648439</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7368,7 +7438,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7399,10 +7469,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131734976</v>
+        <v>131734966</v>
       </c>
       <c r="B64" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7429,7 +7499,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7438,10 +7508,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>654741</v>
+        <v>654763</v>
       </c>
       <c r="R64" t="n">
-        <v>6648393</v>
+        <v>6648431</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7478,7 +7548,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7509,10 +7579,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131735008</v>
+        <v>131734967</v>
       </c>
       <c r="B65" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7548,10 +7618,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>654742</v>
+        <v>654767</v>
       </c>
       <c r="R65" t="n">
-        <v>6648421</v>
+        <v>6648426</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7619,10 +7689,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131734978</v>
+        <v>131734968</v>
       </c>
       <c r="B66" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7649,7 +7719,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -7658,10 +7728,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>654727</v>
+        <v>654757</v>
       </c>
       <c r="R66" t="n">
-        <v>6648373</v>
+        <v>6648426</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7698,7 +7768,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>150</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7729,10 +7799,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131734973</v>
+        <v>131734969</v>
       </c>
       <c r="B67" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7759,7 +7829,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -7768,10 +7838,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>654745</v>
+        <v>654769</v>
       </c>
       <c r="R67" t="n">
-        <v>6648400</v>
+        <v>6648419</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7808,7 +7878,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7839,10 +7909,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131734996</v>
+        <v>131734970</v>
       </c>
       <c r="B68" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7869,7 +7939,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -7878,10 +7948,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>654792</v>
+        <v>654768</v>
       </c>
       <c r="R68" t="n">
-        <v>6648440</v>
+        <v>6648417</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7918,7 +7988,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7949,10 +8019,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131734990</v>
+        <v>131734971</v>
       </c>
       <c r="B69" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7979,7 +8049,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -7988,10 +8058,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>654759</v>
+        <v>654769</v>
       </c>
       <c r="R69" t="n">
-        <v>6648451</v>
+        <v>6648414</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8028,7 +8098,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8059,10 +8129,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131734989</v>
+        <v>131734972</v>
       </c>
       <c r="B70" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8089,19 +8159,19 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Björkhagen Nordost, Upl</t>
+          <t>Björkhagen Öst, Upl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>654712</v>
+        <v>654752</v>
       </c>
       <c r="R70" t="n">
-        <v>6648455</v>
+        <v>6648405</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8138,7 +8208,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8169,10 +8239,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131734958</v>
+        <v>131734973</v>
       </c>
       <c r="B71" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8199,7 +8269,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8208,10 +8278,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>654774</v>
+        <v>654745</v>
       </c>
       <c r="R71" t="n">
-        <v>6648455</v>
+        <v>6648400</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8248,7 +8318,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8279,10 +8349,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131735006</v>
+        <v>131734974</v>
       </c>
       <c r="B72" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8309,7 +8379,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8318,10 +8388,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>654741</v>
+        <v>654744</v>
       </c>
       <c r="R72" t="n">
-        <v>6648426</v>
+        <v>6648398</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8358,7 +8428,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8389,10 +8459,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131734979</v>
+        <v>131734975</v>
       </c>
       <c r="B73" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8419,7 +8489,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8428,10 +8498,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>654727</v>
+        <v>654745</v>
       </c>
       <c r="R73" t="n">
-        <v>6648372</v>
+        <v>6648398</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8468,7 +8538,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8499,10 +8569,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131734962</v>
+        <v>131734976</v>
       </c>
       <c r="B74" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8538,10 +8608,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>654787</v>
+        <v>654741</v>
       </c>
       <c r="R74" t="n">
-        <v>6648429</v>
+        <v>6648393</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8609,10 +8679,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131735003</v>
+        <v>131734977</v>
       </c>
       <c r="B75" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8639,7 +8709,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8648,10 +8718,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>654763</v>
+        <v>654741</v>
       </c>
       <c r="R75" t="n">
-        <v>6648432</v>
+        <v>6648385</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8688,7 +8758,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8719,10 +8789,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131734967</v>
+        <v>131734978</v>
       </c>
       <c r="B76" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8749,7 +8819,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8758,10 +8828,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>654767</v>
+        <v>654727</v>
       </c>
       <c r="R76" t="n">
-        <v>6648426</v>
+        <v>6648373</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8798,7 +8868,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8829,10 +8899,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131734981</v>
+        <v>131734979</v>
       </c>
       <c r="B77" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8859,7 +8929,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8868,10 +8938,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>654730</v>
+        <v>654727</v>
       </c>
       <c r="R77" t="n">
-        <v>6648387</v>
+        <v>6648372</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8908,7 +8978,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8939,10 +9009,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131734965</v>
+        <v>131734980</v>
       </c>
       <c r="B78" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8969,7 +9039,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -8978,10 +9048,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>654766</v>
+        <v>654730</v>
       </c>
       <c r="R78" t="n">
-        <v>6648439</v>
+        <v>6648380</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9018,7 +9088,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9049,10 +9119,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131734993</v>
+        <v>131734981</v>
       </c>
       <c r="B79" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9079,7 +9149,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9088,10 +9158,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>654772</v>
+        <v>654730</v>
       </c>
       <c r="R79" t="n">
-        <v>6648449</v>
+        <v>6648387</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9128,7 +9198,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9162,7 +9232,7 @@
         <v>131734982</v>
       </c>
       <c r="B80" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9269,10 +9339,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131735010</v>
+        <v>131734983</v>
       </c>
       <c r="B81" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9308,10 +9378,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>654751</v>
+        <v>654723</v>
       </c>
       <c r="R81" t="n">
-        <v>6648394</v>
+        <v>6648398</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9379,10 +9449,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131735009</v>
+        <v>131734984</v>
       </c>
       <c r="B82" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9409,7 +9479,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -9418,7 +9488,7 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>654752</v>
+        <v>654718</v>
       </c>
       <c r="R82" t="n">
         <v>6648398</v>
@@ -9458,7 +9528,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9489,10 +9559,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131734956</v>
+        <v>131734985</v>
       </c>
       <c r="B83" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9519,19 +9589,19 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Björkhagen Öst, Upl</t>
+          <t>Björkhagen Nordost, Upl</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>654762</v>
+        <v>654690</v>
       </c>
       <c r="R83" t="n">
-        <v>6648462</v>
+        <v>6648410</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9568,7 +9638,7 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9599,10 +9669,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131735013</v>
+        <v>131734986</v>
       </c>
       <c r="B84" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9629,7 +9699,7 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P84" t="inlineStr">
@@ -9638,10 +9708,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>654673</v>
+        <v>654694</v>
       </c>
       <c r="R84" t="n">
-        <v>6648408</v>
+        <v>6648453</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9678,7 +9748,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9709,10 +9779,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131735002</v>
+        <v>131734987</v>
       </c>
       <c r="B85" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9739,19 +9809,19 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Björkhagen Öst, Upl</t>
+          <t>Björkhagen Nordost, Upl</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>654764</v>
+        <v>654704</v>
       </c>
       <c r="R85" t="n">
-        <v>6648424</v>
+        <v>6648450</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9788,7 +9858,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9819,10 +9889,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131734968</v>
+        <v>131734988</v>
       </c>
       <c r="B86" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9849,19 +9919,19 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Björkhagen Öst, Upl</t>
+          <t>Björkhagen Nordost, Upl</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>654757</v>
+        <v>654715</v>
       </c>
       <c r="R86" t="n">
-        <v>6648426</v>
+        <v>6648463</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9898,7 +9968,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9929,10 +9999,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131734960</v>
+        <v>131734989</v>
       </c>
       <c r="B87" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9959,19 +10029,19 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Björkhagen Öst, Upl</t>
+          <t>Björkhagen Nordost, Upl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>654792</v>
+        <v>654712</v>
       </c>
       <c r="R87" t="n">
-        <v>6648447</v>
+        <v>6648455</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10008,7 +10078,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10039,10 +10109,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131734954</v>
+        <v>131734990</v>
       </c>
       <c r="B88" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10078,10 +10148,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>654763</v>
+        <v>654759</v>
       </c>
       <c r="R88" t="n">
-        <v>6648468</v>
+        <v>6648451</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10149,10 +10219,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131734977</v>
+        <v>131734993</v>
       </c>
       <c r="B89" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10179,7 +10249,7 @@
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10188,10 +10258,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>654741</v>
+        <v>654772</v>
       </c>
       <c r="R89" t="n">
-        <v>6648385</v>
+        <v>6648449</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10228,7 +10298,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10259,10 +10329,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131734991</v>
+        <v>131734995</v>
       </c>
       <c r="B90" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10298,10 +10368,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>654767</v>
+        <v>654772</v>
       </c>
       <c r="R90" t="n">
-        <v>6648447</v>
+        <v>6648453</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10369,10 +10439,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131734988</v>
+        <v>131734996</v>
       </c>
       <c r="B91" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10399,19 +10469,19 @@
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Björkhagen Nordost, Upl</t>
+          <t>Björkhagen Öst, Upl</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>654715</v>
+        <v>654792</v>
       </c>
       <c r="R91" t="n">
-        <v>6648463</v>
+        <v>6648440</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10448,7 +10518,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10479,10 +10549,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>131735001</v>
+        <v>131734997</v>
       </c>
       <c r="B92" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10518,10 +10588,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>654772</v>
+        <v>654786</v>
       </c>
       <c r="R92" t="n">
-        <v>6648432</v>
+        <v>6648440</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10589,10 +10659,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>131734964</v>
+        <v>131734998</v>
       </c>
       <c r="B93" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10628,10 +10698,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>654772</v>
+        <v>654784</v>
       </c>
       <c r="R93" t="n">
-        <v>6648442</v>
+        <v>6648430</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10699,10 +10769,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>131734984</v>
+        <v>131734999</v>
       </c>
       <c r="B94" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10729,7 +10799,7 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P94" t="inlineStr">
@@ -10738,10 +10808,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>654718</v>
+        <v>654777</v>
       </c>
       <c r="R94" t="n">
-        <v>6648398</v>
+        <v>6648431</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10778,7 +10848,7 @@
       </c>
       <c r="AC94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10809,10 +10879,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>131735007</v>
+        <v>131735000</v>
       </c>
       <c r="B95" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10839,7 +10909,7 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P95" t="inlineStr">
@@ -10848,10 +10918,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>654747</v>
+        <v>654772</v>
       </c>
       <c r="R95" t="n">
-        <v>6648424</v>
+        <v>6648435</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10888,7 +10958,7 @@
       </c>
       <c r="AC95" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10919,10 +10989,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131734999</v>
+        <v>131735001</v>
       </c>
       <c r="B96" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10958,10 +11028,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>654777</v>
+        <v>654772</v>
       </c>
       <c r="R96" t="n">
-        <v>6648431</v>
+        <v>6648432</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11029,10 +11099,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>131735017</v>
+        <v>131735002</v>
       </c>
       <c r="B97" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11059,7 +11129,7 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
@@ -11068,10 +11138,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>654780</v>
+        <v>654764</v>
       </c>
       <c r="R97" t="n">
-        <v>6648423</v>
+        <v>6648424</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11108,7 +11178,7 @@
       </c>
       <c r="AC97" t="inlineStr">
         <is>
-          <t>156</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11139,10 +11209,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>131734985</v>
+        <v>131735003</v>
       </c>
       <c r="B98" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11169,19 +11239,19 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Björkhagen Nordost, Upl</t>
+          <t>Björkhagen Öst, Upl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>654690</v>
+        <v>654763</v>
       </c>
       <c r="R98" t="n">
-        <v>6648410</v>
+        <v>6648432</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11218,7 +11288,7 @@
       </c>
       <c r="AC98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11249,10 +11319,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>131734970</v>
+        <v>131735004</v>
       </c>
       <c r="B99" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11279,7 +11349,7 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="P99" t="inlineStr">
@@ -11288,10 +11358,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>654768</v>
+        <v>654763</v>
       </c>
       <c r="R99" t="n">
-        <v>6648417</v>
+        <v>6648435</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11328,7 +11398,7 @@
       </c>
       <c r="AC99" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>70</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11359,10 +11429,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>131734975</v>
+        <v>131735005</v>
       </c>
       <c r="B100" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11389,7 +11459,7 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
@@ -11398,10 +11468,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>654745</v>
+        <v>654755</v>
       </c>
       <c r="R100" t="n">
-        <v>6648398</v>
+        <v>6648433</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11438,7 +11508,7 @@
       </c>
       <c r="AC100" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>100</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11469,10 +11539,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>131734997</v>
+        <v>131735006</v>
       </c>
       <c r="B101" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11499,7 +11569,7 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P101" t="inlineStr">
@@ -11508,10 +11578,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>654786</v>
+        <v>654741</v>
       </c>
       <c r="R101" t="n">
-        <v>6648440</v>
+        <v>6648426</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11548,7 +11618,7 @@
       </c>
       <c r="AC101" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11579,10 +11649,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>131734959</v>
+        <v>131735007</v>
       </c>
       <c r="B102" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11618,10 +11688,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>654781</v>
+        <v>654747</v>
       </c>
       <c r="R102" t="n">
-        <v>6648448</v>
+        <v>6648424</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11689,10 +11759,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>131734983</v>
+        <v>131735008</v>
       </c>
       <c r="B103" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11719,7 +11789,7 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P103" t="inlineStr">
@@ -11728,10 +11798,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>654723</v>
+        <v>654742</v>
       </c>
       <c r="R103" t="n">
-        <v>6648398</v>
+        <v>6648421</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11768,7 +11838,7 @@
       </c>
       <c r="AC103" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11799,10 +11869,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>131734986</v>
+        <v>131735009</v>
       </c>
       <c r="B104" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11829,19 +11899,19 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Björkhagen Nordost, Upl</t>
+          <t>Björkhagen Öst, Upl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>654694</v>
+        <v>654752</v>
       </c>
       <c r="R104" t="n">
-        <v>6648453</v>
+        <v>6648398</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11878,7 +11948,7 @@
       </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>30</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11909,10 +11979,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>131734963</v>
+        <v>131735010</v>
       </c>
       <c r="B105" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11939,7 +12009,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11948,10 +12018,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>654787</v>
+        <v>654751</v>
       </c>
       <c r="R105" t="n">
-        <v>6648437</v>
+        <v>6648394</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11988,7 +12058,7 @@
       </c>
       <c r="AC105" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>20</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12019,10 +12089,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>131735012</v>
+        <v>131735011</v>
       </c>
       <c r="B106" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12058,10 +12128,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>654726</v>
+        <v>654749</v>
       </c>
       <c r="R106" t="n">
-        <v>6648414</v>
+        <v>6648395</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12129,10 +12199,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131734980</v>
+        <v>131735012</v>
       </c>
       <c r="B107" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12159,7 +12229,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -12168,10 +12238,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>654730</v>
+        <v>654726</v>
       </c>
       <c r="R107" t="n">
-        <v>6648380</v>
+        <v>6648414</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12208,7 +12278,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12239,10 +12309,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>131734987</v>
+        <v>131735013</v>
       </c>
       <c r="B108" t="n">
-        <v>99098</v>
+        <v>99195</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12269,7 +12339,7 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
@@ -12278,10 +12348,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>654704</v>
+        <v>654673</v>
       </c>
       <c r="R108" t="n">
-        <v>6648450</v>
+        <v>6648408</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12318,7 +12388,7 @@
       </c>
       <c r="AC108" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12346,6 +12416,1064 @@
           <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
         </is>
       </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>131735017</v>
+      </c>
+      <c r="B109" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Björkhagen Öst, Upl</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>654780</v>
+      </c>
+      <c r="R109" t="n">
+        <v>6648423</v>
+      </c>
+      <c r="S109" t="n">
+        <v>10</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Helene Andersson</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Henrik Tykosson</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Holmen Skog Naturvärdesinventering </t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>132124559</v>
+      </c>
+      <c r="B110" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Kasimirshagen V, Upl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>654866</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6648416</v>
+      </c>
+      <c r="S110" t="n">
+        <v>3</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>08:52</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>127785128</v>
+      </c>
+      <c r="B111" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>654803</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6648362</v>
+      </c>
+      <c r="S111" t="n">
+        <v>8</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>20:12</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>77318206</v>
+      </c>
+      <c r="B112" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Tomta, 1,4 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>654765</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6648265</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>77318207</v>
+      </c>
+      <c r="B113" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Tomta, 1,3 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>654797</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6648275</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>77318200</v>
+      </c>
+      <c r="B114" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Tomta, 1,5 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>654530</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6648283</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2019-04-21</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Henry Åkerström, Thorleif Joelson</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>127053055</v>
+      </c>
+      <c r="B115" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>654681</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6648407</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>127785199</v>
+      </c>
+      <c r="B116" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>654839</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6648361</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>20:17</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>127785252</v>
+      </c>
+      <c r="B117" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Tomta SV om, Upl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>654821</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6648353</v>
+      </c>
+      <c r="S117" t="n">
+        <v>7</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-08-24</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>20:19</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Anders Lindholm</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>129705723</v>
+      </c>
+      <c r="B118" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Tomta, Upl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>654836</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6648344</v>
+      </c>
+      <c r="S118" t="n">
+        <v>15</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Rasbo</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-11-15</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
